--- a/3_PROJECT_DATA/cards.xlsx
+++ b/3_PROJECT_DATA/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/63b0f51049750c05/Desktop/eko_inv/3_PROJECT_DATA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{506DB702-BE4A-4559-8D41-4BA1E1A8A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{677F7910-0C46-45C8-BF71-42D3B904DAA3}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="13_ncr:1_{506DB702-BE4A-4559-8D41-4BA1E1A8A544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76F821BC-7F1B-4C29-BB16-EAA9C14DD32F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3299" uniqueCount="1806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3331" uniqueCount="1825">
   <si>
     <t>Company</t>
   </si>
@@ -5438,6 +5438,63 @@
   </si>
   <si>
     <t>ОБЩИНА ВАРНА - КДР</t>
+  </si>
+  <si>
+    <t>БАРСА 1</t>
+  </si>
+  <si>
+    <t>БАРСА 1 ЕООД</t>
+  </si>
+  <si>
+    <t>БАРСА</t>
+  </si>
+  <si>
+    <t>78970153027722114</t>
+  </si>
+  <si>
+    <t>78970153027722122</t>
+  </si>
+  <si>
+    <t>202878867</t>
+  </si>
+  <si>
+    <t>СИ АГРО 2011 ЕООД</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>201398307</t>
+  </si>
+  <si>
+    <t>ТУБА МФ</t>
+  </si>
+  <si>
+    <t>78970153027722163</t>
+  </si>
+  <si>
+    <t>В9684ХМ</t>
+  </si>
+  <si>
+    <t>78970155027722960</t>
+  </si>
+  <si>
+    <t>TX4225XP</t>
+  </si>
+  <si>
+    <t>78970155027722952</t>
+  </si>
+  <si>
+    <t>СВ9373ОР</t>
+  </si>
+  <si>
+    <t>СВ1462ОС</t>
+  </si>
+  <si>
+    <t>78970153027722148</t>
+  </si>
+  <si>
+    <t>78970153027722155</t>
   </si>
 </sst>
 </file>
@@ -5836,7 +5893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E823"/>
+  <dimension ref="A1:E831"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="70.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -10482,11 +10539,11 @@
       <c r="A332" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="B332" s="2" t="s">
-        <v>1593</v>
+      <c r="B332" s="1" t="s">
+        <v>1821</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>1594</v>
+        <v>1823</v>
       </c>
       <c r="D332" s="3" t="s">
         <v>974</v>
@@ -10496,11 +10553,11 @@
       <c r="A333" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="B333" s="2" t="s">
-        <v>632</v>
+      <c r="B333" s="1" t="s">
+        <v>1822</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>633</v>
+        <v>1824</v>
       </c>
       <c r="D333" s="3" t="s">
         <v>974</v>
@@ -10511,10 +10568,10 @@
         <v>972</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>634</v>
+        <v>1593</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>635</v>
+        <v>1594</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>974</v>
@@ -10525,10 +10582,10 @@
         <v>972</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="D335" s="3" t="s">
         <v>974</v>
@@ -10539,10 +10596,10 @@
         <v>972</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="D336" s="3" t="s">
         <v>974</v>
@@ -10553,10 +10610,10 @@
         <v>972</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="D337" s="3" t="s">
         <v>974</v>
@@ -10567,10 +10624,10 @@
         <v>972</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>974</v>
@@ -10581,10 +10638,10 @@
         <v>972</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="D339" s="3" t="s">
         <v>974</v>
@@ -10595,10 +10652,10 @@
         <v>972</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="D340" s="3" t="s">
         <v>974</v>
@@ -10609,10 +10666,10 @@
         <v>972</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D341" s="3" t="s">
         <v>974</v>
@@ -10623,10 +10680,10 @@
         <v>972</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>1020</v>
+        <v>646</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>1021</v>
+        <v>647</v>
       </c>
       <c r="D342" s="3" t="s">
         <v>974</v>
@@ -10634,13 +10691,13 @@
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D343" s="3" t="s">
         <v>974</v>
@@ -10648,13 +10705,13 @@
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>652</v>
+        <v>1020</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>653</v>
+        <v>1021</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>974</v>
@@ -10665,10 +10722,10 @@
         <v>971</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="D345" s="3" t="s">
         <v>974</v>
@@ -10679,10 +10736,10 @@
         <v>971</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="D346" s="3" t="s">
         <v>974</v>
@@ -10693,10 +10750,10 @@
         <v>971</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="D347" s="3" t="s">
         <v>974</v>
@@ -10707,10 +10764,10 @@
         <v>971</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="D348" s="3" t="s">
         <v>974</v>
@@ -10721,10 +10778,10 @@
         <v>971</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D349" s="3" t="s">
         <v>974</v>
@@ -10735,10 +10792,10 @@
         <v>971</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D350" s="3" t="s">
         <v>974</v>
@@ -10746,30 +10803,30 @@
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.25">
@@ -10777,10 +10834,10 @@
         <v>973</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="D353" s="3" t="s">
         <v>975</v>
@@ -10791,10 +10848,10 @@
         <v>973</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="D354" s="3" t="s">
         <v>975</v>
@@ -10802,30 +10859,30 @@
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.25">
@@ -10833,10 +10890,10 @@
         <v>976</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="D357" s="3" t="s">
         <v>987</v>
@@ -10847,10 +10904,10 @@
         <v>976</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="D358" s="3" t="s">
         <v>987</v>
@@ -10861,10 +10918,10 @@
         <v>976</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="D359" s="3" t="s">
         <v>987</v>
@@ -10875,10 +10932,10 @@
         <v>976</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="D360" s="3" t="s">
         <v>987</v>
@@ -10889,10 +10946,10 @@
         <v>976</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="D361" s="3" t="s">
         <v>987</v>
@@ -10903,10 +10960,10 @@
         <v>976</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="D362" s="3" t="s">
         <v>987</v>
@@ -10917,10 +10974,10 @@
         <v>976</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="D363" s="3" t="s">
         <v>987</v>
@@ -10931,10 +10988,10 @@
         <v>976</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="D364" s="3" t="s">
         <v>987</v>
@@ -10945,10 +11002,10 @@
         <v>976</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="D365" s="3" t="s">
         <v>987</v>
@@ -10959,10 +11016,10 @@
         <v>976</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="D366" s="3" t="s">
         <v>987</v>
@@ -10973,10 +11030,10 @@
         <v>976</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="D367" s="3" t="s">
         <v>987</v>
@@ -10987,10 +11044,10 @@
         <v>976</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="D368" s="3" t="s">
         <v>987</v>
@@ -11001,10 +11058,10 @@
         <v>976</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D369" s="3" t="s">
         <v>987</v>
@@ -11015,10 +11072,10 @@
         <v>976</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="D370" s="3" t="s">
         <v>987</v>
@@ -11026,13 +11083,13 @@
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="D371" s="3" t="s">
         <v>987</v>
@@ -11040,13 +11097,13 @@
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="D372" s="3" t="s">
         <v>987</v>
@@ -11057,10 +11114,10 @@
         <v>977</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="D373" s="3" t="s">
         <v>987</v>
@@ -11071,10 +11128,10 @@
         <v>977</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="D374" s="3" t="s">
         <v>987</v>
@@ -11085,10 +11142,10 @@
         <v>977</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="D375" s="3" t="s">
         <v>987</v>
@@ -11099,10 +11156,10 @@
         <v>977</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>987</v>
@@ -11113,10 +11170,10 @@
         <v>977</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="D377" s="3" t="s">
         <v>987</v>
@@ -11127,10 +11184,10 @@
         <v>977</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="D378" s="3" t="s">
         <v>987</v>
@@ -11141,10 +11198,10 @@
         <v>977</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="D379" s="3" t="s">
         <v>987</v>
@@ -11155,10 +11212,10 @@
         <v>977</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="D380" s="3" t="s">
         <v>987</v>
@@ -11169,10 +11226,10 @@
         <v>977</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="D381" s="3" t="s">
         <v>987</v>
@@ -11183,10 +11240,10 @@
         <v>977</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="D382" s="3" t="s">
         <v>987</v>
@@ -11197,10 +11254,10 @@
         <v>977</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="D383" s="3" t="s">
         <v>987</v>
@@ -11211,10 +11268,10 @@
         <v>977</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="D384" s="3" t="s">
         <v>987</v>
@@ -11225,10 +11282,10 @@
         <v>977</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="D385" s="3" t="s">
         <v>987</v>
@@ -11239,10 +11296,10 @@
         <v>977</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="D386" s="3" t="s">
         <v>987</v>
@@ -11250,41 +11307,41 @@
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>893</v>
+        <v>735</v>
       </c>
       <c r="D387" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
-        <v>984</v>
+        <v>977</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D388" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>742</v>
+        <v>893</v>
       </c>
       <c r="D389" s="3" t="s">
         <v>986</v>
@@ -11295,10 +11352,10 @@
         <v>984</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="D390" s="3" t="s">
         <v>986</v>
@@ -11309,10 +11366,10 @@
         <v>984</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C391" s="2" t="s">
-        <v>875</v>
+        <v>742</v>
       </c>
       <c r="D391" s="3" t="s">
         <v>986</v>
@@ -11323,10 +11380,10 @@
         <v>984</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C392" s="2" t="s">
-        <v>876</v>
+        <v>744</v>
       </c>
       <c r="D392" s="3" t="s">
         <v>986</v>
@@ -11337,10 +11394,10 @@
         <v>984</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="C393" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>986</v>
@@ -11348,13 +11405,13 @@
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="C394" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>986</v>
@@ -11362,13 +11419,13 @@
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C395" s="2" t="s">
-        <v>746</v>
+        <v>877</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>986</v>
@@ -11376,30 +11433,30 @@
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C396" s="2" t="s">
-        <v>788</v>
+        <v>878</v>
       </c>
       <c r="D396" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C397" s="2" t="s">
-        <v>810</v>
+        <v>746</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.25">
@@ -11407,10 +11464,10 @@
         <v>978</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C398" s="2" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="D398" s="3" t="s">
         <v>988</v>
@@ -11421,10 +11478,10 @@
         <v>978</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C399" s="2" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>988</v>
@@ -11435,10 +11492,10 @@
         <v>978</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C400" s="2" t="s">
-        <v>800</v>
+        <v>787</v>
       </c>
       <c r="D400" s="3" t="s">
         <v>988</v>
@@ -11449,10 +11506,10 @@
         <v>978</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>899</v>
+        <v>807</v>
       </c>
       <c r="D401" s="3" t="s">
         <v>988</v>
@@ -11463,10 +11520,10 @@
         <v>978</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D402" s="3" t="s">
         <v>988</v>
@@ -11477,10 +11534,10 @@
         <v>978</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>790</v>
+        <v>899</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>988</v>
@@ -11491,10 +11548,10 @@
         <v>978</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D404" s="3" t="s">
         <v>988</v>
@@ -11505,10 +11562,10 @@
         <v>978</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>751</v>
+        <v>790</v>
       </c>
       <c r="D405" s="3" t="s">
         <v>988</v>
@@ -11519,10 +11576,10 @@
         <v>978</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="D406" s="3" t="s">
         <v>988</v>
@@ -11533,10 +11590,10 @@
         <v>978</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>805</v>
+        <v>751</v>
       </c>
       <c r="D407" s="3" t="s">
         <v>988</v>
@@ -11547,10 +11604,10 @@
         <v>978</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>751</v>
+        <v>803</v>
       </c>
       <c r="D408" s="3" t="s">
         <v>988</v>
@@ -11561,10 +11618,10 @@
         <v>978</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>762</v>
+        <v>805</v>
       </c>
       <c r="D409" s="3" t="s">
         <v>988</v>
@@ -11575,10 +11632,10 @@
         <v>978</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>809</v>
+        <v>751</v>
       </c>
       <c r="D410" s="3" t="s">
         <v>988</v>
@@ -11589,10 +11646,10 @@
         <v>978</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>898</v>
+        <v>762</v>
       </c>
       <c r="D411" s="3" t="s">
         <v>988</v>
@@ -11603,10 +11660,10 @@
         <v>978</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>791</v>
+        <v>809</v>
       </c>
       <c r="D412" s="3" t="s">
         <v>988</v>
@@ -11617,10 +11674,10 @@
         <v>978</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>812</v>
+        <v>898</v>
       </c>
       <c r="D413" s="3" t="s">
         <v>988</v>
@@ -11631,10 +11688,10 @@
         <v>978</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D414" s="3" t="s">
         <v>988</v>
@@ -11645,10 +11702,10 @@
         <v>978</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>838</v>
+        <v>812</v>
       </c>
       <c r="D415" s="3" t="s">
         <v>988</v>
@@ -11659,10 +11716,10 @@
         <v>978</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>808</v>
+        <v>792</v>
       </c>
       <c r="D416" s="3" t="s">
         <v>988</v>
@@ -11673,10 +11730,10 @@
         <v>978</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>795</v>
+        <v>838</v>
       </c>
       <c r="D417" s="3" t="s">
         <v>988</v>
@@ -11687,10 +11744,10 @@
         <v>978</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C418" s="2" t="s">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="D418" s="3" t="s">
         <v>988</v>
@@ -11701,10 +11758,10 @@
         <v>978</v>
       </c>
       <c r="B419" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C419" s="2" t="s">
-        <v>1583</v>
+        <v>795</v>
       </c>
       <c r="D419" s="3" t="s">
         <v>988</v>
@@ -11715,10 +11772,10 @@
         <v>978</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>811</v>
+        <v>793</v>
       </c>
       <c r="D420" s="3" t="s">
         <v>988</v>
@@ -11729,10 +11786,10 @@
         <v>978</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C421" s="2" t="s">
-        <v>802</v>
+        <v>1583</v>
       </c>
       <c r="D421" s="3" t="s">
         <v>988</v>
@@ -11743,10 +11800,10 @@
         <v>978</v>
       </c>
       <c r="B422" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C422" s="2" t="s">
-        <v>1578</v>
+        <v>811</v>
       </c>
       <c r="D422" s="3" t="s">
         <v>988</v>
@@ -11757,10 +11814,10 @@
         <v>978</v>
       </c>
       <c r="B423" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C423" s="2" t="s">
-        <v>1579</v>
+        <v>802</v>
       </c>
       <c r="D423" s="3" t="s">
         <v>988</v>
@@ -11771,10 +11828,10 @@
         <v>978</v>
       </c>
       <c r="B424" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C424" s="2" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="D424" s="3" t="s">
         <v>988</v>
@@ -11785,10 +11842,10 @@
         <v>978</v>
       </c>
       <c r="B425" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C425" s="2" t="s">
-        <v>804</v>
+        <v>1579</v>
       </c>
       <c r="D425" s="3" t="s">
         <v>988</v>
@@ -11799,10 +11856,10 @@
         <v>978</v>
       </c>
       <c r="B426" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C426" s="2" t="s">
-        <v>794</v>
+        <v>1580</v>
       </c>
       <c r="D426" s="3" t="s">
         <v>988</v>
@@ -11813,10 +11870,10 @@
         <v>978</v>
       </c>
       <c r="B427" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C427" s="2" t="s">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="D427" s="3" t="s">
         <v>988</v>
@@ -11827,10 +11884,10 @@
         <v>978</v>
       </c>
       <c r="B428" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C428" s="2" t="s">
-        <v>806</v>
+        <v>794</v>
       </c>
       <c r="D428" s="3" t="s">
         <v>988</v>
@@ -11841,10 +11898,10 @@
         <v>978</v>
       </c>
       <c r="B429" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C429" s="2" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="D429" s="3" t="s">
         <v>988</v>
@@ -11854,11 +11911,11 @@
       <c r="A430" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B430" s="4" t="s">
-        <v>783</v>
+      <c r="B430" s="2" t="s">
+        <v>781</v>
       </c>
       <c r="C430" s="2" t="s">
-        <v>896</v>
+        <v>806</v>
       </c>
       <c r="D430" s="3" t="s">
         <v>988</v>
@@ -11869,10 +11926,10 @@
         <v>978</v>
       </c>
       <c r="B431" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C431" s="2" t="s">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="D431" s="3" t="s">
         <v>988</v>
@@ -11882,11 +11939,11 @@
       <c r="A432" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B432" s="2" t="s">
-        <v>785</v>
+      <c r="B432" s="4" t="s">
+        <v>783</v>
       </c>
       <c r="C432" s="2" t="s">
-        <v>798</v>
+        <v>896</v>
       </c>
       <c r="D432" s="3" t="s">
         <v>988</v>
@@ -11897,10 +11954,10 @@
         <v>978</v>
       </c>
       <c r="B433" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C433" s="2" t="s">
-        <v>1581</v>
+        <v>796</v>
       </c>
       <c r="D433" s="3" t="s">
         <v>988</v>
@@ -11911,10 +11968,10 @@
         <v>978</v>
       </c>
       <c r="B434" s="2" t="s">
-        <v>1582</v>
+        <v>785</v>
       </c>
       <c r="C434" s="2" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="D434" s="3" t="s">
         <v>988</v>
@@ -11922,44 +11979,44 @@
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="B435" s="5" t="s">
-        <v>826</v>
+        <v>978</v>
+      </c>
+      <c r="B435" s="2" t="s">
+        <v>786</v>
       </c>
       <c r="C435" s="2" t="s">
-        <v>814</v>
+        <v>1581</v>
       </c>
       <c r="D435" s="3" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="B436" s="5" t="s">
-        <v>827</v>
+        <v>978</v>
+      </c>
+      <c r="B436" s="2" t="s">
+        <v>1582</v>
       </c>
       <c r="C436" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="D436" s="3" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="B437" s="5" t="s">
-        <v>828</v>
+        <v>978</v>
+      </c>
+      <c r="B437" s="2" t="s">
+        <v>1819</v>
       </c>
       <c r="C437" s="2" t="s">
-        <v>816</v>
+        <v>1820</v>
       </c>
       <c r="D437" s="3" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.25">
@@ -11967,10 +12024,10 @@
         <v>979</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D438" s="3" t="s">
         <v>980</v>
@@ -11981,10 +12038,10 @@
         <v>979</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C439" s="2" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D439" s="3" t="s">
         <v>980</v>
@@ -11995,10 +12052,10 @@
         <v>979</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C440" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="D440" s="3" t="s">
         <v>980</v>
@@ -12009,10 +12066,10 @@
         <v>979</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C441" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D441" s="3" t="s">
         <v>980</v>
@@ -12023,10 +12080,10 @@
         <v>979</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C442" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D442" s="3" t="s">
         <v>980</v>
@@ -12037,10 +12094,10 @@
         <v>979</v>
       </c>
       <c r="B443" s="5" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C443" s="2" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="D443" s="3" t="s">
         <v>980</v>
@@ -12051,10 +12108,10 @@
         <v>979</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C444" s="2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="D444" s="3" t="s">
         <v>980</v>
@@ -12065,10 +12122,10 @@
         <v>979</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C445" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D445" s="3" t="s">
         <v>980</v>
@@ -12079,10 +12136,10 @@
         <v>979</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="C446" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D446" s="3" t="s">
         <v>980</v>
@@ -12090,44 +12147,44 @@
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="B447" s="2" t="s">
-        <v>843</v>
+        <v>979</v>
+      </c>
+      <c r="B447" s="5" t="s">
+        <v>835</v>
       </c>
       <c r="C447" s="2" t="s">
-        <v>884</v>
+        <v>823</v>
       </c>
       <c r="D447" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="B448" s="2" t="s">
-        <v>840</v>
+        <v>979</v>
+      </c>
+      <c r="B448" s="5" t="s">
+        <v>836</v>
       </c>
       <c r="C448" s="2" t="s">
-        <v>847</v>
+        <v>824</v>
       </c>
       <c r="D448" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
-        <v>839</v>
-      </c>
-      <c r="B449" s="2" t="s">
-        <v>841</v>
+        <v>979</v>
+      </c>
+      <c r="B449" s="5" t="s">
+        <v>837</v>
       </c>
       <c r="C449" s="2" t="s">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="D449" s="3" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
@@ -12135,10 +12192,10 @@
         <v>839</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C450" s="2" t="s">
-        <v>846</v>
+        <v>884</v>
       </c>
       <c r="D450" s="3" t="s">
         <v>981</v>
@@ -12149,10 +12206,10 @@
         <v>839</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C451" s="2" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D451" s="3" t="s">
         <v>981</v>
@@ -12163,10 +12220,10 @@
         <v>839</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C452" s="2" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D452" s="3" t="s">
         <v>981</v>
@@ -12177,10 +12234,10 @@
         <v>839</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>871</v>
+        <v>842</v>
       </c>
       <c r="C453" s="2" t="s">
-        <v>870</v>
+        <v>846</v>
       </c>
       <c r="D453" s="3" t="s">
         <v>981</v>
@@ -12188,70 +12245,61 @@
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="B454" s="2">
-        <v>3</v>
+        <v>839</v>
+      </c>
+      <c r="B454" s="2" t="s">
+        <v>843</v>
       </c>
       <c r="C454" s="2" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="D454" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="E454" s="3" t="s">
-        <v>850</v>
+        <v>981</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
-        <v>880</v>
+        <v>839</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>1584</v>
+        <v>844</v>
       </c>
       <c r="C455" s="2" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="D455" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="E455" s="3" t="s">
-        <v>852</v>
+        <v>981</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
-        <v>880</v>
+        <v>839</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>856</v>
+        <v>871</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="D456" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="E456" s="3" t="s">
-        <v>854</v>
+        <v>981</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B457" s="2" t="s">
-        <v>859</v>
+      <c r="B457" s="2">
+        <v>3</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>858</v>
+        <v>851</v>
       </c>
       <c r="D457" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>857</v>
+        <v>850</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
@@ -12259,16 +12307,16 @@
         <v>880</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>860</v>
+        <v>1584</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="D458" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E458" s="3" t="s">
-        <v>879</v>
+        <v>852</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
@@ -12276,16 +12324,16 @@
         <v>880</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>50</v>
+        <v>856</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="D459" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E459" s="3" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
@@ -12293,16 +12341,16 @@
         <v>880</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>173</v>
+        <v>859</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D460" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E460" s="3" t="s">
-        <v>865</v>
+        <v>857</v>
       </c>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
@@ -12310,30 +12358,33 @@
         <v>880</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>176</v>
+        <v>860</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="D461" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E461" s="3" t="s">
-        <v>866</v>
+        <v>879</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>880</v>
       </c>
+      <c r="B462" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="C462" s="2" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="D462" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E462" s="3" t="s">
-        <v>869</v>
+        <v>861</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
@@ -12341,33 +12392,33 @@
         <v>880</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="D463" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E463" s="3" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B464" s="4" t="s">
-        <v>883</v>
+      <c r="B464" s="2" t="s">
+        <v>176</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>881</v>
+        <v>867</v>
       </c>
       <c r="D464" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E464" s="3" t="s">
-        <v>882</v>
+        <v>866</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
@@ -12375,95 +12426,101 @@
         <v>880</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>886</v>
+        <v>868</v>
       </c>
       <c r="D465" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E465" s="3" t="s">
-        <v>887</v>
+        <v>869</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>880</v>
       </c>
+      <c r="B466" s="2" t="s">
+        <v>184</v>
+      </c>
       <c r="C466" s="2" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="D466" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E466" s="3" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>880</v>
       </c>
+      <c r="B467" s="4" t="s">
+        <v>883</v>
+      </c>
       <c r="C467" s="2" t="s">
-        <v>1804</v>
+        <v>881</v>
       </c>
       <c r="D467" s="3" t="s">
         <v>982</v>
       </c>
-      <c r="E467" s="3"/>
+      <c r="E467" s="3" t="s">
+        <v>882</v>
+      </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>880</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>894</v>
+        <v>886</v>
       </c>
       <c r="D468" s="3" t="s">
         <v>982</v>
       </c>
       <c r="E468" s="3" t="s">
-        <v>866</v>
+        <v>887</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="B469" s="2" t="s">
-        <v>1005</v>
+        <v>880</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>993</v>
+        <v>888</v>
       </c>
       <c r="D469" s="3" t="s">
-        <v>1017</v>
+        <v>982</v>
+      </c>
+      <c r="E469" s="3" t="s">
+        <v>889</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="B470" s="2" t="s">
-        <v>1006</v>
+        <v>880</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>994</v>
+        <v>1804</v>
       </c>
       <c r="D470" s="3" t="s">
-        <v>1017</v>
-      </c>
+        <v>982</v>
+      </c>
+      <c r="E470" s="3"/>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="B471" s="2" t="s">
-        <v>1013</v>
+        <v>880</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>995</v>
+        <v>894</v>
       </c>
       <c r="D471" s="3" t="s">
-        <v>1017</v>
+        <v>982</v>
+      </c>
+      <c r="E471" s="3" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
@@ -12471,10 +12528,10 @@
         <v>992</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="D472" s="3" t="s">
         <v>1017</v>
@@ -12485,10 +12542,10 @@
         <v>992</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="D473" s="3" t="s">
         <v>1017</v>
@@ -12499,10 +12556,10 @@
         <v>992</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="C474" s="2" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="D474" s="3" t="s">
         <v>1017</v>
@@ -12513,10 +12570,10 @@
         <v>992</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="D475" s="3" t="s">
         <v>1017</v>
@@ -12527,10 +12584,10 @@
         <v>992</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="D476" s="3" t="s">
         <v>1017</v>
@@ -12541,10 +12598,10 @@
         <v>992</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="D477" s="3" t="s">
         <v>1017</v>
@@ -12555,10 +12612,10 @@
         <v>992</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="D478" s="3" t="s">
         <v>1017</v>
@@ -12569,10 +12626,10 @@
         <v>992</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="C479" s="2" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="D479" s="3" t="s">
         <v>1017</v>
@@ -12583,69 +12640,69 @@
         <v>992</v>
       </c>
       <c r="B480" s="2" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="C480" s="2" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="D480" s="3" t="s">
         <v>1017</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A481" s="3" t="s">
-        <v>1018</v>
+      <c r="A481" s="1" t="s">
+        <v>992</v>
       </c>
       <c r="B481" s="2" t="s">
-        <v>180</v>
+        <v>1014</v>
       </c>
       <c r="C481" s="2" t="s">
-        <v>872</v>
+        <v>1002</v>
       </c>
       <c r="D481" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
-        <v>1034</v>
+        <v>992</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>1022</v>
-      </c>
-      <c r="C482" s="6" t="s">
-        <v>1095</v>
+        <v>1015</v>
+      </c>
+      <c r="C482" s="2" t="s">
+        <v>1003</v>
       </c>
       <c r="D482" s="3" t="s">
-        <v>1033</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
-        <v>1034</v>
+        <v>992</v>
       </c>
       <c r="B483" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C483" s="6" t="s">
-        <v>1096</v>
+        <v>1016</v>
+      </c>
+      <c r="C483" s="2" t="s">
+        <v>1004</v>
       </c>
       <c r="D483" s="3" t="s">
-        <v>1033</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A484" s="1" t="s">
-        <v>1034</v>
+      <c r="A484" s="3" t="s">
+        <v>1018</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C484" s="6" t="s">
-        <v>1097</v>
+        <v>180</v>
+      </c>
+      <c r="C484" s="2" t="s">
+        <v>872</v>
       </c>
       <c r="D484" s="3" t="s">
-        <v>1033</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.25">
@@ -12653,10 +12710,10 @@
         <v>1034</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="D485" s="3" t="s">
         <v>1033</v>
@@ -12667,10 +12724,10 @@
         <v>1034</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>1099</v>
+        <v>1096</v>
       </c>
       <c r="D486" s="3" t="s">
         <v>1033</v>
@@ -12681,10 +12738,10 @@
         <v>1034</v>
       </c>
       <c r="B487" s="2" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="D487" s="3" t="s">
         <v>1033</v>
@@ -12695,10 +12752,10 @@
         <v>1034</v>
       </c>
       <c r="B488" s="2" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="D488" s="3" t="s">
         <v>1033</v>
@@ -12709,10 +12766,10 @@
         <v>1034</v>
       </c>
       <c r="B489" s="2" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="D489" s="3" t="s">
         <v>1033</v>
@@ -12723,10 +12780,10 @@
         <v>1034</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="D490" s="3" t="s">
         <v>1033</v>
@@ -12737,10 +12794,10 @@
         <v>1034</v>
       </c>
       <c r="B491" s="2" t="s">
-        <v>1031</v>
+        <v>1028</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="D491" s="3" t="s">
         <v>1033</v>
@@ -12751,10 +12808,10 @@
         <v>1034</v>
       </c>
       <c r="B492" s="2" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>1105</v>
+        <v>1102</v>
       </c>
       <c r="D492" s="3" t="s">
         <v>1033</v>
@@ -12762,44 +12819,44 @@
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B493" s="2" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="C493" s="6" t="s">
-        <v>1106</v>
+        <v>1103</v>
       </c>
       <c r="D493" s="3" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="C494" s="6" t="s">
-        <v>1107</v>
+        <v>1104</v>
       </c>
       <c r="D494" s="3" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>1039</v>
+        <v>1032</v>
       </c>
       <c r="C495" s="6" t="s">
-        <v>1108</v>
+        <v>1105</v>
       </c>
       <c r="D495" s="3" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.25">
@@ -12807,10 +12864,10 @@
         <v>1035</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="C496" s="6" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="D496" s="3" t="s">
         <v>1036</v>
@@ -12821,10 +12878,10 @@
         <v>1035</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C497" s="6" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="D497" s="3" t="s">
         <v>1036</v>
@@ -12835,10 +12892,10 @@
         <v>1035</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="C498" s="6" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="D498" s="3" t="s">
         <v>1036</v>
@@ -12849,10 +12906,10 @@
         <v>1035</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="C499" s="6" t="s">
-        <v>1112</v>
+        <v>1109</v>
       </c>
       <c r="D499" s="3" t="s">
         <v>1036</v>
@@ -12863,10 +12920,10 @@
         <v>1035</v>
       </c>
       <c r="B500" s="2" t="s">
-        <v>1044</v>
+        <v>1041</v>
       </c>
       <c r="C500" s="6" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="D500" s="3" t="s">
         <v>1036</v>
@@ -12877,10 +12934,10 @@
         <v>1035</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1045</v>
+        <v>1042</v>
       </c>
       <c r="C501" s="6" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="D501" s="3" t="s">
         <v>1036</v>
@@ -12888,86 +12945,86 @@
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
-        <v>1591</v>
+        <v>1035</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="C502" s="6" t="s">
-        <v>1115</v>
+        <v>1112</v>
       </c>
       <c r="D502" s="3" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
-        <v>1591</v>
+        <v>1035</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C503" s="6" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="D503" s="3" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
-        <v>1591</v>
+        <v>1035</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="C504" s="6" t="s">
-        <v>1117</v>
+        <v>1114</v>
       </c>
       <c r="D504" s="3" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
-        <v>1055</v>
+        <v>1591</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1051</v>
+        <v>1048</v>
       </c>
       <c r="C505" s="6" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="D505" s="3" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
-        <v>1055</v>
+        <v>1591</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C506" s="6" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="D506" s="3" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
-        <v>1055</v>
+        <v>1591</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="C507" s="6" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="D507" s="3" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.25">
@@ -12975,10 +13032,10 @@
         <v>1055</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1054</v>
+        <v>1051</v>
       </c>
       <c r="C508" s="6" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="D508" s="3" t="s">
         <v>1050</v>
@@ -12986,86 +13043,86 @@
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="C509" s="6" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="D509" s="3" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="C510" s="6" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="D510" s="3" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C511" s="6" t="s">
-        <v>1124</v>
+        <v>1121</v>
       </c>
       <c r="D511" s="3" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B512" s="2" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="C512" s="6" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="D512" s="3" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="C513" s="6" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="D513" s="3" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="B514" s="2" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="C514" s="6" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="D514" s="3" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.25">
@@ -13073,10 +13130,10 @@
         <v>1060</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="C515" s="6" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="D515" s="3" t="s">
         <v>1061</v>
@@ -13087,10 +13144,10 @@
         <v>1060</v>
       </c>
       <c r="B516" s="2" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="C516" s="6" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="D516" s="3" t="s">
         <v>1061</v>
@@ -13101,10 +13158,10 @@
         <v>1060</v>
       </c>
       <c r="B517" s="2" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="C517" s="6" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="D517" s="3" t="s">
         <v>1061</v>
@@ -13115,10 +13172,10 @@
         <v>1060</v>
       </c>
       <c r="B518" s="2" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="C518" s="6" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="D518" s="3" t="s">
         <v>1061</v>
@@ -13129,10 +13186,10 @@
         <v>1060</v>
       </c>
       <c r="B519" s="2" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="C519" s="6" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="D519" s="3" t="s">
         <v>1061</v>
@@ -13143,10 +13200,10 @@
         <v>1060</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="C520" s="6" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="D520" s="3" t="s">
         <v>1061</v>
@@ -13157,10 +13214,10 @@
         <v>1060</v>
       </c>
       <c r="B521" s="2" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="C521" s="6" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="D521" s="3" t="s">
         <v>1061</v>
@@ -13171,10 +13228,10 @@
         <v>1060</v>
       </c>
       <c r="B522" s="2" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="C522" s="6" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="D522" s="3" t="s">
         <v>1061</v>
@@ -13182,86 +13239,86 @@
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="C523" s="6" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="D523" s="3" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="B524" s="2" t="s">
-        <v>1589</v>
-      </c>
-      <c r="C524" s="3" t="s">
-        <v>1590</v>
+        <v>1071</v>
+      </c>
+      <c r="C524" s="6" t="s">
+        <v>1134</v>
       </c>
       <c r="D524" s="3" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
-        <v>1073</v>
+        <v>1060</v>
       </c>
       <c r="B525" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="C525" s="3" t="s">
-        <v>1634</v>
+        <v>1072</v>
+      </c>
+      <c r="C525" s="6" t="s">
+        <v>1135</v>
       </c>
       <c r="D525" s="3" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B526" s="2" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="C526" s="6" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D526" s="3" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C527" s="6" t="s">
-        <v>1138</v>
+        <v>1589</v>
+      </c>
+      <c r="C527" s="3" t="s">
+        <v>1590</v>
       </c>
       <c r="D527" s="3" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
-        <v>1076</v>
+        <v>1073</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>1079</v>
-      </c>
-      <c r="C528" s="6" t="s">
-        <v>1139</v>
+        <v>1633</v>
+      </c>
+      <c r="C528" s="3" t="s">
+        <v>1634</v>
       </c>
       <c r="D528" s="3" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.25">
@@ -13269,10 +13326,10 @@
         <v>1076</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>1801</v>
+        <v>1077</v>
       </c>
       <c r="C529" s="6" t="s">
-        <v>1802</v>
+        <v>1137</v>
       </c>
       <c r="D529" s="3" t="s">
         <v>1081</v>
@@ -13283,10 +13340,10 @@
         <v>1076</v>
       </c>
       <c r="B530" s="2" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="C530" s="6" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="D530" s="3" t="s">
         <v>1081</v>
@@ -13294,44 +13351,44 @@
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="B531" s="2" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="C531" s="6" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="D531" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>1085</v>
+        <v>1801</v>
       </c>
       <c r="C532" s="6" t="s">
-        <v>1142</v>
+        <v>1802</v>
       </c>
       <c r="D532" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="B533" s="2" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="C533" s="6" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="D533" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.25">
@@ -13339,10 +13396,10 @@
         <v>1082</v>
       </c>
       <c r="B534" s="2" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="C534" s="6" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="D534" s="3" t="s">
         <v>1083</v>
@@ -13353,10 +13410,10 @@
         <v>1082</v>
       </c>
       <c r="B535" s="2" t="s">
-        <v>1088</v>
+        <v>1085</v>
       </c>
       <c r="C535" s="6" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="D535" s="3" t="s">
         <v>1083</v>
@@ -13364,44 +13421,44 @@
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
-        <v>1540</v>
+        <v>1082</v>
       </c>
       <c r="B536" s="2" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="C536" s="6" t="s">
-        <v>1146</v>
+        <v>1143</v>
       </c>
       <c r="D536" s="3" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
-        <v>1540</v>
+        <v>1082</v>
       </c>
       <c r="B537" s="2" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="C537" s="6" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="D537" s="3" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
-        <v>1540</v>
+        <v>1082</v>
       </c>
       <c r="B538" s="2" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="C538" s="6" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="D538" s="3" t="s">
-        <v>1094</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.25">
@@ -13409,10 +13466,10 @@
         <v>1540</v>
       </c>
       <c r="B539" s="2" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="C539" s="6" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="D539" s="3" t="s">
         <v>1094</v>
@@ -13423,10 +13480,10 @@
         <v>1540</v>
       </c>
       <c r="B540" s="2" t="s">
-        <v>1093</v>
+        <v>1090</v>
       </c>
       <c r="C540" s="6" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="D540" s="3" t="s">
         <v>1094</v>
@@ -13434,184 +13491,184 @@
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
-        <v>1151</v>
+        <v>1540</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C541" s="2" t="s">
-        <v>1168</v>
+        <v>1091</v>
+      </c>
+      <c r="C541" s="6" t="s">
+        <v>1148</v>
       </c>
       <c r="D541" s="3" t="s">
-        <v>1459</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
-        <v>1151</v>
+        <v>1540</v>
       </c>
       <c r="B542" s="2" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C542" s="2" t="s">
-        <v>1169</v>
+        <v>1092</v>
+      </c>
+      <c r="C542" s="6" t="s">
+        <v>1149</v>
       </c>
       <c r="D542" s="3" t="s">
-        <v>1459</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
-        <v>1152</v>
+        <v>1540</v>
       </c>
       <c r="B543" s="2" t="s">
-        <v>1170</v>
-      </c>
-      <c r="C543" s="2" t="s">
-        <v>1172</v>
+        <v>1093</v>
+      </c>
+      <c r="C543" s="6" t="s">
+        <v>1150</v>
       </c>
       <c r="D543" s="3" t="s">
-        <v>1460</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B544" s="2" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="C544" s="2" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="D544" s="3" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B545" s="2" t="s">
-        <v>1174</v>
+        <v>1167</v>
       </c>
       <c r="C545" s="2" t="s">
-        <v>1176</v>
+        <v>1169</v>
       </c>
       <c r="D545" s="3" t="s">
-        <v>1461</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B546" s="2" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="C546" s="2" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="D546" s="3" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>1178</v>
+        <v>1171</v>
       </c>
       <c r="C547" s="2" t="s">
-        <v>1180</v>
+        <v>1173</v>
       </c>
       <c r="D547" s="3" t="s">
-        <v>1462</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="C548" s="2" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="D548" s="3" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>1182</v>
+        <v>1175</v>
       </c>
       <c r="C549" s="2" t="s">
-        <v>1184</v>
+        <v>1177</v>
       </c>
       <c r="D549" s="3" t="s">
-        <v>1463</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="C550" s="2" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="D550" s="3" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>1186</v>
+        <v>1179</v>
       </c>
       <c r="C551" s="2" t="s">
-        <v>1190</v>
+        <v>1181</v>
       </c>
       <c r="D551" s="3" t="s">
-        <v>1464</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="C552" s="2" t="s">
-        <v>1191</v>
+        <v>1184</v>
       </c>
       <c r="D552" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="C553" s="2" t="s">
-        <v>1192</v>
+        <v>1185</v>
       </c>
       <c r="D553" s="3" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.25">
@@ -13619,10 +13676,10 @@
         <v>1156</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="C554" s="2" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="D554" s="3" t="s">
         <v>1464</v>
@@ -13630,72 +13687,72 @@
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>1194</v>
+        <v>1187</v>
       </c>
       <c r="C555" s="2" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="D555" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B556" s="2" t="s">
-        <v>1195</v>
+        <v>1188</v>
       </c>
       <c r="C556" s="2" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="D556" s="3" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B557" s="7" t="s">
-        <v>1234</v>
+        <v>1156</v>
+      </c>
+      <c r="B557" s="2" t="s">
+        <v>1189</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="D557" s="3" t="s">
-        <v>1466</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B558" s="7" t="s">
-        <v>1235</v>
+        <v>1157</v>
+      </c>
+      <c r="B558" s="2" t="s">
+        <v>1194</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="D558" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="B559" s="7" t="s">
-        <v>1236</v>
+        <v>1157</v>
+      </c>
+      <c r="B559" s="2" t="s">
+        <v>1195</v>
       </c>
       <c r="C559" s="2" t="s">
-        <v>1200</v>
+        <v>1197</v>
       </c>
       <c r="D559" s="3" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.25">
@@ -13703,10 +13760,10 @@
         <v>1158</v>
       </c>
       <c r="B560" s="7" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="C560" s="2" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="D560" s="3" t="s">
         <v>1466</v>
@@ -13717,10 +13774,10 @@
         <v>1158</v>
       </c>
       <c r="B561" s="7" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="C561" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="D561" s="3" t="s">
         <v>1466</v>
@@ -13731,10 +13788,10 @@
         <v>1158</v>
       </c>
       <c r="B562" s="7" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="D562" s="3" t="s">
         <v>1466</v>
@@ -13745,10 +13802,10 @@
         <v>1158</v>
       </c>
       <c r="B563" s="7" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C563" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D563" s="3" t="s">
         <v>1466</v>
@@ -13759,10 +13816,10 @@
         <v>1158</v>
       </c>
       <c r="B564" s="7" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C564" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D564" s="3" t="s">
         <v>1466</v>
@@ -13773,10 +13830,10 @@
         <v>1158</v>
       </c>
       <c r="B565" s="7" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C565" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D565" s="3" t="s">
         <v>1466</v>
@@ -13787,10 +13844,10 @@
         <v>1158</v>
       </c>
       <c r="B566" s="7" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C566" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="D566" s="3" t="s">
         <v>1466</v>
@@ -13801,10 +13858,10 @@
         <v>1158</v>
       </c>
       <c r="B567" s="7" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="C567" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="D567" s="3" t="s">
         <v>1466</v>
@@ -13815,10 +13872,10 @@
         <v>1158</v>
       </c>
       <c r="B568" s="7" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="C568" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="D568" s="3" t="s">
         <v>1466</v>
@@ -13829,10 +13886,10 @@
         <v>1158</v>
       </c>
       <c r="B569" s="7" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C569" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="D569" s="3" t="s">
         <v>1466</v>
@@ -13843,10 +13900,10 @@
         <v>1158</v>
       </c>
       <c r="B570" s="7" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="C570" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="D570" s="3" t="s">
         <v>1466</v>
@@ -13857,10 +13914,10 @@
         <v>1158</v>
       </c>
       <c r="B571" s="7" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="C571" s="2" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D571" s="3" t="s">
         <v>1466</v>
@@ -13871,10 +13928,10 @@
         <v>1158</v>
       </c>
       <c r="B572" s="7" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="D572" s="3" t="s">
         <v>1466</v>
@@ -13885,10 +13942,10 @@
         <v>1158</v>
       </c>
       <c r="B573" s="7" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="C573" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="D573" s="3" t="s">
         <v>1466</v>
@@ -13899,10 +13956,10 @@
         <v>1158</v>
       </c>
       <c r="B574" s="7" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="C574" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="D574" s="3" t="s">
         <v>1466</v>
@@ -13913,10 +13970,10 @@
         <v>1158</v>
       </c>
       <c r="B575" s="7" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="C575" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="D575" s="3" t="s">
         <v>1466</v>
@@ -13927,10 +13984,10 @@
         <v>1158</v>
       </c>
       <c r="B576" s="7" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="C576" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="D576" s="3" t="s">
         <v>1466</v>
@@ -13941,10 +13998,10 @@
         <v>1158</v>
       </c>
       <c r="B577" s="7" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="C577" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D577" s="3" t="s">
         <v>1466</v>
@@ -13955,10 +14012,10 @@
         <v>1158</v>
       </c>
       <c r="B578" s="7" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C578" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="D578" s="3" t="s">
         <v>1466</v>
@@ -13968,11 +14025,11 @@
       <c r="A579" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B579" s="4" t="s">
-        <v>1256</v>
+      <c r="B579" s="7" t="s">
+        <v>1255</v>
       </c>
       <c r="C579" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="D579" s="3" t="s">
         <v>1466</v>
@@ -13982,11 +14039,11 @@
       <c r="A580" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B580" s="7" t="s">
-        <v>1257</v>
+      <c r="B580" s="4" t="s">
+        <v>1256</v>
       </c>
       <c r="C580" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D580" s="3" t="s">
         <v>1466</v>
@@ -13997,10 +14054,10 @@
         <v>1158</v>
       </c>
       <c r="B581" s="7" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="D581" s="3" t="s">
         <v>1466</v>
@@ -14011,10 +14068,10 @@
         <v>1158</v>
       </c>
       <c r="B582" s="7" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="C582" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="D582" s="3" t="s">
         <v>1466</v>
@@ -14025,10 +14082,10 @@
         <v>1158</v>
       </c>
       <c r="B583" s="7" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="D583" s="3" t="s">
         <v>1466</v>
@@ -14039,10 +14096,10 @@
         <v>1158</v>
       </c>
       <c r="B584" s="7" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C584" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D584" s="3" t="s">
         <v>1466</v>
@@ -14053,10 +14110,10 @@
         <v>1158</v>
       </c>
       <c r="B585" s="7" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C585" s="2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D585" s="3" t="s">
         <v>1466</v>
@@ -14067,10 +14124,10 @@
         <v>1158</v>
       </c>
       <c r="B586" s="7" t="s">
-        <v>1232</v>
+        <v>1262</v>
       </c>
       <c r="C586" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D586" s="3" t="s">
         <v>1466</v>
@@ -14081,10 +14138,10 @@
         <v>1158</v>
       </c>
       <c r="B587" s="7" t="s">
-        <v>1263</v>
+        <v>1232</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D587" s="3" t="s">
         <v>1466</v>
@@ -14095,10 +14152,10 @@
         <v>1158</v>
       </c>
       <c r="B588" s="7" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="D588" s="3" t="s">
         <v>1466</v>
@@ -14109,10 +14166,10 @@
         <v>1158</v>
       </c>
       <c r="B589" s="7" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="C589" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="D589" s="3" t="s">
         <v>1466</v>
@@ -14123,10 +14180,10 @@
         <v>1158</v>
       </c>
       <c r="B590" s="7" t="s">
-        <v>1765</v>
+        <v>1265</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>1767</v>
+        <v>1230</v>
       </c>
       <c r="D590" s="3" t="s">
         <v>1466</v>
@@ -14137,10 +14194,10 @@
         <v>1158</v>
       </c>
       <c r="B591" s="7" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="D591" s="3" t="s">
         <v>1466</v>
@@ -14151,10 +14208,10 @@
         <v>1158</v>
       </c>
       <c r="B592" s="7" t="s">
-        <v>1233</v>
+        <v>1766</v>
       </c>
       <c r="C592" s="2" t="s">
-        <v>1231</v>
+        <v>1768</v>
       </c>
       <c r="D592" s="3" t="s">
         <v>1466</v>
@@ -14162,16 +14219,16 @@
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B593" s="7" t="s">
-        <v>1266</v>
+        <v>1233</v>
       </c>
       <c r="C593" s="2" t="s">
-        <v>1282</v>
+        <v>1231</v>
       </c>
       <c r="D593" s="3" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.25">
@@ -14179,10 +14236,10 @@
         <v>1159</v>
       </c>
       <c r="B594" s="7" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C594" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="D594" s="3" t="s">
         <v>1467</v>
@@ -14193,10 +14250,10 @@
         <v>1159</v>
       </c>
       <c r="B595" s="7" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C595" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D595" s="3" t="s">
         <v>1467</v>
@@ -14207,10 +14264,10 @@
         <v>1159</v>
       </c>
       <c r="B596" s="7" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="C596" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D596" s="3" t="s">
         <v>1467</v>
@@ -14221,10 +14278,10 @@
         <v>1159</v>
       </c>
       <c r="B597" s="7" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="C597" s="2" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D597" s="3" t="s">
         <v>1467</v>
@@ -14235,10 +14292,10 @@
         <v>1159</v>
       </c>
       <c r="B598" s="7" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D598" s="3" t="s">
         <v>1467</v>
@@ -14249,10 +14306,10 @@
         <v>1159</v>
       </c>
       <c r="B599" s="7" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D599" s="3" t="s">
         <v>1467</v>
@@ -14263,10 +14320,10 @@
         <v>1159</v>
       </c>
       <c r="B600" s="7" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C600" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="D600" s="3" t="s">
         <v>1467</v>
@@ -14277,10 +14334,10 @@
         <v>1159</v>
       </c>
       <c r="B601" s="7" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="D601" s="3" t="s">
         <v>1467</v>
@@ -14291,10 +14348,10 @@
         <v>1159</v>
       </c>
       <c r="B602" s="7" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D602" s="3" t="s">
         <v>1467</v>
@@ -14305,10 +14362,10 @@
         <v>1159</v>
       </c>
       <c r="B603" s="7" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="C603" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D603" s="3" t="s">
         <v>1467</v>
@@ -14319,10 +14376,10 @@
         <v>1159</v>
       </c>
       <c r="B604" s="7" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="C604" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D604" s="3" t="s">
         <v>1467</v>
@@ -14333,10 +14390,10 @@
         <v>1159</v>
       </c>
       <c r="B605" s="7" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D605" s="3" t="s">
         <v>1467</v>
@@ -14347,10 +14404,10 @@
         <v>1159</v>
       </c>
       <c r="B606" s="7" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D606" s="3" t="s">
         <v>1467</v>
@@ -14361,10 +14418,10 @@
         <v>1159</v>
       </c>
       <c r="B607" s="7" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="D607" s="3" t="s">
         <v>1467</v>
@@ -14375,10 +14432,10 @@
         <v>1159</v>
       </c>
       <c r="B608" s="7" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D608" s="3" t="s">
         <v>1467</v>
@@ -14386,16 +14443,16 @@
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="B609" s="7" t="s">
-        <v>1298</v>
+        <v>1281</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="D609" s="3" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
@@ -14403,10 +14460,10 @@
         <v>1160</v>
       </c>
       <c r="B610" s="7" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="C610" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D610" s="3" t="s">
         <v>1468</v>
@@ -14417,10 +14474,10 @@
         <v>1160</v>
       </c>
       <c r="B611" s="7" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D611" s="3" t="s">
         <v>1468</v>
@@ -14431,10 +14488,10 @@
         <v>1160</v>
       </c>
       <c r="B612" s="7" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="C612" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D612" s="3" t="s">
         <v>1468</v>
@@ -14442,30 +14499,30 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B613" s="2" t="s">
-        <v>1306</v>
+        <v>1160</v>
+      </c>
+      <c r="B613" s="7" t="s">
+        <v>1301</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>1558</v>
+        <v>1305</v>
       </c>
       <c r="D613" s="3" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>1576</v>
+        <v>1558</v>
       </c>
       <c r="D614" s="3" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.25">
@@ -14473,10 +14530,10 @@
         <v>1162</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="D615" s="3" t="s">
         <v>1470</v>
@@ -14484,27 +14541,27 @@
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="B616" s="7" t="s">
-        <v>1309</v>
-      </c>
-      <c r="C616" s="8" t="s">
-        <v>1560</v>
+        <v>1162</v>
+      </c>
+      <c r="B616" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C616" s="2" t="s">
+        <v>1577</v>
       </c>
       <c r="D616" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>1587</v>
       </c>
-      <c r="B617" s="7" t="s">
-        <v>1310</v>
-      </c>
-      <c r="C617" s="8" t="s">
-        <v>1561</v>
+      <c r="B617" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C617" s="2" t="s">
+        <v>1818</v>
       </c>
       <c r="D617" s="3" t="s">
         <v>1471</v>
@@ -14515,10 +14572,10 @@
         <v>1587</v>
       </c>
       <c r="B618" s="7" t="s">
-        <v>1311</v>
-      </c>
-      <c r="C618" s="8" t="s">
-        <v>1562</v>
+        <v>1235</v>
+      </c>
+      <c r="C618" s="2" t="s">
+        <v>1199</v>
       </c>
       <c r="D618" s="3" t="s">
         <v>1471</v>
@@ -14529,10 +14586,10 @@
         <v>1587</v>
       </c>
       <c r="B619" s="7" t="s">
-        <v>1312</v>
-      </c>
-      <c r="C619" s="8" t="s">
-        <v>1563</v>
+        <v>1236</v>
+      </c>
+      <c r="C619" s="2" t="s">
+        <v>1200</v>
       </c>
       <c r="D619" s="3" t="s">
         <v>1471</v>
@@ -14543,10 +14600,10 @@
         <v>1587</v>
       </c>
       <c r="B620" s="7" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="C620" s="8" t="s">
-        <v>1554</v>
+        <v>1560</v>
       </c>
       <c r="D620" s="3" t="s">
         <v>1471</v>
@@ -14557,10 +14614,10 @@
         <v>1587</v>
       </c>
       <c r="B621" s="7" t="s">
-        <v>1314</v>
+        <v>1310</v>
       </c>
       <c r="C621" s="8" t="s">
-        <v>1564</v>
+        <v>1561</v>
       </c>
       <c r="D621" s="3" t="s">
         <v>1471</v>
@@ -14571,10 +14628,10 @@
         <v>1587</v>
       </c>
       <c r="B622" s="7" t="s">
-        <v>1315</v>
+        <v>1311</v>
       </c>
       <c r="C622" s="8" t="s">
-        <v>1565</v>
+        <v>1562</v>
       </c>
       <c r="D622" s="3" t="s">
         <v>1471</v>
@@ -14585,10 +14642,10 @@
         <v>1587</v>
       </c>
       <c r="B623" s="7" t="s">
-        <v>1316</v>
+        <v>1312</v>
       </c>
       <c r="C623" s="8" t="s">
-        <v>1553</v>
+        <v>1563</v>
       </c>
       <c r="D623" s="3" t="s">
         <v>1471</v>
@@ -14599,10 +14656,10 @@
         <v>1587</v>
       </c>
       <c r="B624" s="7" t="s">
-        <v>1317</v>
+        <v>1313</v>
       </c>
       <c r="C624" s="8" t="s">
-        <v>1566</v>
+        <v>1554</v>
       </c>
       <c r="D624" s="3" t="s">
         <v>1471</v>
@@ -14613,10 +14670,10 @@
         <v>1587</v>
       </c>
       <c r="B625" s="7" t="s">
-        <v>1318</v>
+        <v>1314</v>
       </c>
       <c r="C625" s="8" t="s">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="D625" s="3" t="s">
         <v>1471</v>
@@ -14627,10 +14684,10 @@
         <v>1587</v>
       </c>
       <c r="B626" s="7" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="C626" s="8" t="s">
-        <v>1568</v>
+        <v>1565</v>
       </c>
       <c r="D626" s="3" t="s">
         <v>1471</v>
@@ -14641,10 +14698,10 @@
         <v>1587</v>
       </c>
       <c r="B627" s="7" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="C627" s="8" t="s">
-        <v>1569</v>
+        <v>1553</v>
       </c>
       <c r="D627" s="3" t="s">
         <v>1471</v>
@@ -14655,10 +14712,10 @@
         <v>1587</v>
       </c>
       <c r="B628" s="7" t="s">
-        <v>1321</v>
+        <v>1317</v>
       </c>
       <c r="C628" s="8" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
       <c r="D628" s="3" t="s">
         <v>1471</v>
@@ -14669,10 +14726,10 @@
         <v>1587</v>
       </c>
       <c r="B629" s="7" t="s">
-        <v>1322</v>
+        <v>1318</v>
       </c>
       <c r="C629" s="8" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="D629" s="3" t="s">
         <v>1471</v>
@@ -14683,10 +14740,10 @@
         <v>1587</v>
       </c>
       <c r="B630" s="7" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="C630" s="8" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="D630" s="3" t="s">
         <v>1471</v>
@@ -14697,10 +14754,10 @@
         <v>1587</v>
       </c>
       <c r="B631" s="7" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C631" s="9" t="s">
-        <v>1362</v>
+        <v>1320</v>
+      </c>
+      <c r="C631" s="8" t="s">
+        <v>1569</v>
       </c>
       <c r="D631" s="3" t="s">
         <v>1471</v>
@@ -14711,10 +14768,10 @@
         <v>1587</v>
       </c>
       <c r="B632" s="7" t="s">
-        <v>1324</v>
-      </c>
-      <c r="C632" s="10" t="s">
-        <v>1363</v>
+        <v>1321</v>
+      </c>
+      <c r="C632" s="8" t="s">
+        <v>1570</v>
       </c>
       <c r="D632" s="3" t="s">
         <v>1471</v>
@@ -14725,10 +14782,10 @@
         <v>1587</v>
       </c>
       <c r="B633" s="7" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C633" s="9" t="s">
-        <v>1364</v>
+        <v>1322</v>
+      </c>
+      <c r="C633" s="8" t="s">
+        <v>1571</v>
       </c>
       <c r="D633" s="3" t="s">
         <v>1471</v>
@@ -14739,10 +14796,10 @@
         <v>1587</v>
       </c>
       <c r="B634" s="7" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C634" s="10" t="s">
-        <v>1365</v>
+        <v>1323</v>
+      </c>
+      <c r="C634" s="8" t="s">
+        <v>1572</v>
       </c>
       <c r="D634" s="3" t="s">
         <v>1471</v>
@@ -14753,10 +14810,10 @@
         <v>1587</v>
       </c>
       <c r="B635" s="7" t="s">
-        <v>1327</v>
+        <v>1077</v>
       </c>
       <c r="C635" s="9" t="s">
-        <v>1366</v>
+        <v>1362</v>
       </c>
       <c r="D635" s="3" t="s">
         <v>1471</v>
@@ -14767,10 +14824,10 @@
         <v>1587</v>
       </c>
       <c r="B636" s="7" t="s">
-        <v>1328</v>
+        <v>1324</v>
       </c>
       <c r="C636" s="10" t="s">
-        <v>1367</v>
+        <v>1363</v>
       </c>
       <c r="D636" s="3" t="s">
         <v>1471</v>
@@ -14781,10 +14838,10 @@
         <v>1587</v>
       </c>
       <c r="B637" s="7" t="s">
-        <v>1329</v>
+        <v>1325</v>
       </c>
       <c r="C637" s="9" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="D637" s="3" t="s">
         <v>1471</v>
@@ -14795,10 +14852,10 @@
         <v>1587</v>
       </c>
       <c r="B638" s="7" t="s">
-        <v>1330</v>
+        <v>1326</v>
       </c>
       <c r="C638" s="10" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="D638" s="3" t="s">
         <v>1471</v>
@@ -14809,10 +14866,10 @@
         <v>1587</v>
       </c>
       <c r="B639" s="7" t="s">
-        <v>1331</v>
+        <v>1327</v>
       </c>
       <c r="C639" s="9" t="s">
-        <v>1370</v>
+        <v>1366</v>
       </c>
       <c r="D639" s="3" t="s">
         <v>1471</v>
@@ -14823,10 +14880,10 @@
         <v>1587</v>
       </c>
       <c r="B640" s="7" t="s">
-        <v>1332</v>
+        <v>1328</v>
       </c>
       <c r="C640" s="10" t="s">
-        <v>1371</v>
+        <v>1367</v>
       </c>
       <c r="D640" s="3" t="s">
         <v>1471</v>
@@ -14837,10 +14894,10 @@
         <v>1587</v>
       </c>
       <c r="B641" s="7" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="C641" s="9" t="s">
-        <v>1372</v>
+        <v>1368</v>
       </c>
       <c r="D641" s="3" t="s">
         <v>1471</v>
@@ -14851,10 +14908,10 @@
         <v>1587</v>
       </c>
       <c r="B642" s="7" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="C642" s="10" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="D642" s="3" t="s">
         <v>1471</v>
@@ -14865,10 +14922,10 @@
         <v>1587</v>
       </c>
       <c r="B643" s="7" t="s">
-        <v>1335</v>
+        <v>1331</v>
       </c>
       <c r="C643" s="9" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="D643" s="3" t="s">
         <v>1471</v>
@@ -14879,10 +14936,10 @@
         <v>1587</v>
       </c>
       <c r="B644" s="7" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="C644" s="10" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="D644" s="3" t="s">
         <v>1471</v>
@@ -14893,10 +14950,10 @@
         <v>1587</v>
       </c>
       <c r="B645" s="7" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="C645" s="9" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="D645" s="3" t="s">
         <v>1471</v>
@@ -14907,10 +14964,10 @@
         <v>1587</v>
       </c>
       <c r="B646" s="7" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="C646" s="10" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="D646" s="3" t="s">
         <v>1471</v>
@@ -14921,10 +14978,10 @@
         <v>1587</v>
       </c>
       <c r="B647" s="7" t="s">
-        <v>1339</v>
+        <v>1335</v>
       </c>
       <c r="C647" s="9" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="D647" s="3" t="s">
         <v>1471</v>
@@ -14935,10 +14992,10 @@
         <v>1587</v>
       </c>
       <c r="B648" s="7" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="C648" s="10" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="D648" s="3" t="s">
         <v>1471</v>
@@ -14949,10 +15006,10 @@
         <v>1587</v>
       </c>
       <c r="B649" s="7" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C649" s="9" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="D649" s="3" t="s">
         <v>1471</v>
@@ -14963,10 +15020,10 @@
         <v>1587</v>
       </c>
       <c r="B650" s="7" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="C650" s="10" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="D650" s="3" t="s">
         <v>1471</v>
@@ -14977,10 +15034,10 @@
         <v>1587</v>
       </c>
       <c r="B651" s="7" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="C651" s="9" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="D651" s="3" t="s">
         <v>1471</v>
@@ -14991,10 +15048,10 @@
         <v>1587</v>
       </c>
       <c r="B652" s="7" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="C652" s="10" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="D652" s="3" t="s">
         <v>1471</v>
@@ -15005,10 +15062,10 @@
         <v>1587</v>
       </c>
       <c r="B653" s="7" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="C653" s="9" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="D653" s="3" t="s">
         <v>1471</v>
@@ -15019,10 +15076,10 @@
         <v>1587</v>
       </c>
       <c r="B654" s="7" t="s">
-        <v>1346</v>
+        <v>1342</v>
       </c>
       <c r="C654" s="10" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="D654" s="3" t="s">
         <v>1471</v>
@@ -15033,10 +15090,10 @@
         <v>1587</v>
       </c>
       <c r="B655" s="7" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="C655" s="9" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="D655" s="3" t="s">
         <v>1471</v>
@@ -15047,10 +15104,10 @@
         <v>1587</v>
       </c>
       <c r="B656" s="7" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="C656" s="10" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="D656" s="3" t="s">
         <v>1471</v>
@@ -15061,10 +15118,10 @@
         <v>1587</v>
       </c>
       <c r="B657" s="7" t="s">
-        <v>1349</v>
+        <v>1345</v>
       </c>
       <c r="C657" s="9" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="D657" s="3" t="s">
         <v>1471</v>
@@ -15075,10 +15132,10 @@
         <v>1587</v>
       </c>
       <c r="B658" s="7" t="s">
-        <v>1350</v>
+        <v>1346</v>
       </c>
       <c r="C658" s="10" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="D658" s="3" t="s">
         <v>1471</v>
@@ -15089,10 +15146,10 @@
         <v>1587</v>
       </c>
       <c r="B659" s="7" t="s">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="C659" s="9" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="D659" s="3" t="s">
         <v>1471</v>
@@ -15103,10 +15160,10 @@
         <v>1587</v>
       </c>
       <c r="B660" s="7" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="C660" s="10" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="D660" s="3" t="s">
         <v>1471</v>
@@ -15117,10 +15174,10 @@
         <v>1587</v>
       </c>
       <c r="B661" s="7" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="C661" s="9" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="D661" s="3" t="s">
         <v>1471</v>
@@ -15131,10 +15188,10 @@
         <v>1587</v>
       </c>
       <c r="B662" s="7" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="C662" s="10" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="D662" s="3" t="s">
         <v>1471</v>
@@ -15145,10 +15202,10 @@
         <v>1587</v>
       </c>
       <c r="B663" s="7" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C663" s="9" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="D663" s="3" t="s">
         <v>1471</v>
@@ -15159,10 +15216,10 @@
         <v>1587</v>
       </c>
       <c r="B664" s="7" t="s">
-        <v>1356</v>
+        <v>1352</v>
       </c>
       <c r="C664" s="10" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="D664" s="3" t="s">
         <v>1471</v>
@@ -15173,10 +15230,10 @@
         <v>1587</v>
       </c>
       <c r="B665" s="7" t="s">
-        <v>1357</v>
+        <v>1353</v>
       </c>
       <c r="C665" s="9" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="D665" s="3" t="s">
         <v>1471</v>
@@ -15187,10 +15244,10 @@
         <v>1587</v>
       </c>
       <c r="B666" s="7" t="s">
-        <v>1358</v>
+        <v>1354</v>
       </c>
       <c r="C666" s="10" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="D666" s="3" t="s">
         <v>1471</v>
@@ -15201,10 +15258,10 @@
         <v>1587</v>
       </c>
       <c r="B667" s="7" t="s">
-        <v>1359</v>
+        <v>1355</v>
       </c>
       <c r="C667" s="9" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="D667" s="3" t="s">
         <v>1471</v>
@@ -15215,10 +15272,10 @@
         <v>1587</v>
       </c>
       <c r="B668" s="7" t="s">
-        <v>1360</v>
+        <v>1356</v>
       </c>
       <c r="C668" s="10" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="D668" s="3" t="s">
         <v>1471</v>
@@ -15229,10 +15286,10 @@
         <v>1587</v>
       </c>
       <c r="B669" s="7" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C669" s="2" t="s">
-        <v>1573</v>
+        <v>1357</v>
+      </c>
+      <c r="C669" s="9" t="s">
+        <v>1396</v>
       </c>
       <c r="D669" s="3" t="s">
         <v>1471</v>
@@ -15240,13 +15297,13 @@
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B670" s="2" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C670" s="8" t="s">
-        <v>1545</v>
+        <v>1587</v>
+      </c>
+      <c r="B670" s="7" t="s">
+        <v>1358</v>
+      </c>
+      <c r="C670" s="10" t="s">
+        <v>1397</v>
       </c>
       <c r="D670" s="3" t="s">
         <v>1471</v>
@@ -15254,13 +15311,13 @@
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B671" s="2" t="s">
-        <v>1401</v>
-      </c>
-      <c r="C671" s="8" t="s">
-        <v>1546</v>
+        <v>1587</v>
+      </c>
+      <c r="B671" s="7" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C671" s="9" t="s">
+        <v>1398</v>
       </c>
       <c r="D671" s="3" t="s">
         <v>1471</v>
@@ -15268,13 +15325,13 @@
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B672" s="2" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C672" s="8" t="s">
-        <v>1547</v>
+        <v>1587</v>
+      </c>
+      <c r="B672" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="C672" s="10" t="s">
+        <v>1399</v>
       </c>
       <c r="D672" s="3" t="s">
         <v>1471</v>
@@ -15282,13 +15339,13 @@
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>1472</v>
-      </c>
-      <c r="B673" s="2" t="s">
-        <v>1403</v>
-      </c>
-      <c r="C673" s="8" t="s">
-        <v>1548</v>
+        <v>1587</v>
+      </c>
+      <c r="B673" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C673" s="2" t="s">
+        <v>1573</v>
       </c>
       <c r="D673" s="3" t="s">
         <v>1471</v>
@@ -15299,10 +15356,10 @@
         <v>1472</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="C674" s="8" t="s">
-        <v>1549</v>
+        <v>1545</v>
       </c>
       <c r="D674" s="3" t="s">
         <v>1471</v>
@@ -15313,10 +15370,10 @@
         <v>1472</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="C675" s="8" t="s">
-        <v>1550</v>
+        <v>1546</v>
       </c>
       <c r="D675" s="3" t="s">
         <v>1471</v>
@@ -15327,10 +15384,10 @@
         <v>1472</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="C676" s="8" t="s">
-        <v>1551</v>
+        <v>1547</v>
       </c>
       <c r="D676" s="3" t="s">
         <v>1471</v>
@@ -15341,10 +15398,10 @@
         <v>1472</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="C677" s="8" t="s">
-        <v>1552</v>
+        <v>1548</v>
       </c>
       <c r="D677" s="3" t="s">
         <v>1471</v>
@@ -15352,13 +15409,13 @@
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>1585</v>
+        <v>1472</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="C678" s="8" t="s">
-        <v>1574</v>
+        <v>1549</v>
       </c>
       <c r="D678" s="3" t="s">
         <v>1471</v>
@@ -15366,13 +15423,13 @@
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>1586</v>
+        <v>1472</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C679" s="9" t="s">
-        <v>1410</v>
+        <v>1405</v>
+      </c>
+      <c r="C679" s="8" t="s">
+        <v>1550</v>
       </c>
       <c r="D679" s="3" t="s">
         <v>1471</v>
@@ -15380,13 +15437,13 @@
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>1592</v>
+        <v>1472</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1450</v>
-      </c>
-      <c r="C680" s="10" t="s">
-        <v>1452</v>
+        <v>1406</v>
+      </c>
+      <c r="C680" s="8" t="s">
+        <v>1551</v>
       </c>
       <c r="D680" s="3" t="s">
         <v>1471</v>
@@ -15394,13 +15451,13 @@
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>1592</v>
+        <v>1472</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1451</v>
-      </c>
-      <c r="C681" s="9" t="s">
-        <v>1453</v>
+        <v>1407</v>
+      </c>
+      <c r="C681" s="8" t="s">
+        <v>1552</v>
       </c>
       <c r="D681" s="3" t="s">
         <v>1471</v>
@@ -15408,13 +15465,13 @@
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>1475</v>
+        <v>1585</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1409</v>
-      </c>
-      <c r="C682" s="2" t="s">
-        <v>1454</v>
+        <v>1408</v>
+      </c>
+      <c r="C682" s="8" t="s">
+        <v>1574</v>
       </c>
       <c r="D682" s="3" t="s">
         <v>1471</v>
@@ -15422,13 +15479,13 @@
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>1805</v>
+        <v>1586</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C683" s="2" t="s">
-        <v>1785</v>
+        <v>1409</v>
+      </c>
+      <c r="C683" s="9" t="s">
+        <v>1410</v>
       </c>
       <c r="D683" s="3" t="s">
         <v>1471</v>
@@ -15436,13 +15493,13 @@
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
-        <v>1805</v>
+        <v>1592</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1780</v>
-      </c>
-      <c r="C684" s="2" t="s">
-        <v>1786</v>
+        <v>1450</v>
+      </c>
+      <c r="C684" s="10" t="s">
+        <v>1452</v>
       </c>
       <c r="D684" s="3" t="s">
         <v>1471</v>
@@ -15450,13 +15507,13 @@
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>1805</v>
+        <v>1592</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1781</v>
-      </c>
-      <c r="C685" s="2" t="s">
-        <v>1787</v>
+        <v>1451</v>
+      </c>
+      <c r="C685" s="9" t="s">
+        <v>1453</v>
       </c>
       <c r="D685" s="3" t="s">
         <v>1471</v>
@@ -15464,13 +15521,13 @@
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>1805</v>
+        <v>1475</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1782</v>
+        <v>1409</v>
       </c>
       <c r="C686" s="2" t="s">
-        <v>1778</v>
+        <v>1454</v>
       </c>
       <c r="D686" s="3" t="s">
         <v>1471</v>
@@ -15481,10 +15538,10 @@
         <v>1805</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1783</v>
+        <v>1779</v>
       </c>
       <c r="C687" s="2" t="s">
-        <v>1788</v>
+        <v>1785</v>
       </c>
       <c r="D687" s="3" t="s">
         <v>1471</v>
@@ -15495,10 +15552,10 @@
         <v>1805</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>1784</v>
+        <v>1780</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>1789</v>
+        <v>1786</v>
       </c>
       <c r="D688" s="3" t="s">
         <v>1471</v>
@@ -15506,86 +15563,86 @@
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>1163</v>
+        <v>1805</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>1411</v>
+        <v>1781</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>1412</v>
+        <v>1787</v>
       </c>
       <c r="D689" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>1163</v>
+        <v>1805</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>1479</v>
-      </c>
-      <c r="C690" s="9" t="s">
-        <v>1575</v>
+        <v>1782</v>
+      </c>
+      <c r="C690" s="2" t="s">
+        <v>1778</v>
       </c>
       <c r="D690" s="3" t="s">
-        <v>1473</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>1164</v>
+        <v>1805</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>1414</v>
-      </c>
-      <c r="C691" s="10" t="s">
-        <v>1429</v>
+        <v>1783</v>
+      </c>
+      <c r="C691" s="2" t="s">
+        <v>1788</v>
       </c>
       <c r="D691" s="3" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>1164</v>
+        <v>1805</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C692" s="9" t="s">
-        <v>1430</v>
+        <v>1784</v>
+      </c>
+      <c r="C692" s="2" t="s">
+        <v>1789</v>
       </c>
       <c r="D692" s="3" t="s">
-        <v>1474</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C693" s="10" t="s">
-        <v>1431</v>
+        <v>1411</v>
+      </c>
+      <c r="C693" s="2" t="s">
+        <v>1412</v>
       </c>
       <c r="D693" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>1418</v>
+        <v>1479</v>
       </c>
       <c r="C694" s="9" t="s">
-        <v>1432</v>
+        <v>1575</v>
       </c>
       <c r="D694" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.25">
@@ -15593,10 +15650,10 @@
         <v>1164</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="C695" s="10" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="D695" s="3" t="s">
         <v>1474</v>
@@ -15607,10 +15664,10 @@
         <v>1164</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="C696" s="9" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="D696" s="3" t="s">
         <v>1474</v>
@@ -15621,10 +15678,10 @@
         <v>1164</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="C697" s="10" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="D697" s="3" t="s">
         <v>1474</v>
@@ -15635,10 +15692,10 @@
         <v>1164</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="C698" s="9" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="D698" s="3" t="s">
         <v>1474</v>
@@ -15649,10 +15706,10 @@
         <v>1164</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="C699" s="10" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="D699" s="3" t="s">
         <v>1474</v>
@@ -15663,10 +15720,10 @@
         <v>1164</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="C700" s="9" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="D700" s="3" t="s">
         <v>1474</v>
@@ -15677,10 +15734,10 @@
         <v>1164</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="C701" s="10" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="D701" s="3" t="s">
         <v>1474</v>
@@ -15691,10 +15748,10 @@
         <v>1164</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="C702" s="9" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="D702" s="3" t="s">
         <v>1474</v>
@@ -15705,10 +15762,10 @@
         <v>1164</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="C703" s="10" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="D703" s="3" t="s">
         <v>1474</v>
@@ -15719,10 +15776,10 @@
         <v>1164</v>
       </c>
       <c r="B704" s="2" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="C704" s="9" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="D704" s="3" t="s">
         <v>1474</v>
@@ -15733,10 +15790,10 @@
         <v>1164</v>
       </c>
       <c r="B705" s="2" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="C705" s="10" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="D705" s="3" t="s">
         <v>1474</v>
@@ -15747,10 +15804,10 @@
         <v>1164</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1413</v>
+        <v>1426</v>
       </c>
       <c r="C706" s="9" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="D706" s="3" t="s">
         <v>1474</v>
@@ -15761,10 +15818,10 @@
         <v>1164</v>
       </c>
       <c r="B707" s="2" t="s">
-        <v>1415</v>
+        <v>1427</v>
       </c>
       <c r="C707" s="10" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="D707" s="3" t="s">
         <v>1474</v>
@@ -15772,58 +15829,58 @@
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>1446</v>
-      </c>
-      <c r="C708" s="2" t="s">
-        <v>1455</v>
+        <v>1428</v>
+      </c>
+      <c r="C708" s="9" t="s">
+        <v>1442</v>
       </c>
       <c r="D708" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>1447</v>
-      </c>
-      <c r="C709" s="2" t="s">
-        <v>1456</v>
+        <v>1423</v>
+      </c>
+      <c r="C709" s="10" t="s">
+        <v>1443</v>
       </c>
       <c r="D709" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B710" s="2" t="s">
-        <v>1448</v>
-      </c>
-      <c r="C710" s="2" t="s">
-        <v>1457</v>
+        <v>1413</v>
+      </c>
+      <c r="C710" s="9" t="s">
+        <v>1444</v>
       </c>
       <c r="D710" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B711" s="2" t="s">
-        <v>1629</v>
-      </c>
-      <c r="C711" s="2" t="s">
-        <v>1630</v>
+        <v>1415</v>
+      </c>
+      <c r="C711" s="10" t="s">
+        <v>1445</v>
       </c>
       <c r="D711" s="3" t="s">
-        <v>1476</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.25">
@@ -15831,10 +15888,10 @@
         <v>1165</v>
       </c>
       <c r="B712" s="2" t="s">
-        <v>1449</v>
+        <v>1446</v>
       </c>
       <c r="C712" s="2" t="s">
-        <v>1458</v>
+        <v>1455</v>
       </c>
       <c r="D712" s="3" t="s">
         <v>1476</v>
@@ -15842,58 +15899,58 @@
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B713" s="2" t="s">
-        <v>1510</v>
+        <v>1447</v>
       </c>
       <c r="C713" s="2" t="s">
-        <v>1480</v>
+        <v>1456</v>
       </c>
       <c r="D713" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B714" s="2" t="s">
-        <v>1511</v>
+        <v>1448</v>
       </c>
       <c r="C714" s="2" t="s">
-        <v>1481</v>
+        <v>1457</v>
       </c>
       <c r="D714" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B715" s="2" t="s">
-        <v>1512</v>
+        <v>1629</v>
       </c>
       <c r="C715" s="2" t="s">
-        <v>1482</v>
+        <v>1630</v>
       </c>
       <c r="D715" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
-        <v>1477</v>
+        <v>1165</v>
       </c>
       <c r="B716" s="2" t="s">
-        <v>1513</v>
+        <v>1449</v>
       </c>
       <c r="C716" s="2" t="s">
-        <v>1483</v>
+        <v>1458</v>
       </c>
       <c r="D716" s="3" t="s">
-        <v>1539</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.25">
@@ -15901,10 +15958,10 @@
         <v>1477</v>
       </c>
       <c r="B717" s="2" t="s">
-        <v>1514</v>
+        <v>1510</v>
       </c>
       <c r="C717" s="2" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="D717" s="3" t="s">
         <v>1539</v>
@@ -15915,10 +15972,10 @@
         <v>1477</v>
       </c>
       <c r="B718" s="2" t="s">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="C718" s="2" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="D718" s="3" t="s">
         <v>1539</v>
@@ -15929,10 +15986,10 @@
         <v>1477</v>
       </c>
       <c r="B719" s="2" t="s">
-        <v>1516</v>
+        <v>1512</v>
       </c>
       <c r="C719" s="2" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="D719" s="3" t="s">
         <v>1539</v>
@@ -15943,10 +16000,10 @@
         <v>1477</v>
       </c>
       <c r="B720" s="2" t="s">
-        <v>1517</v>
+        <v>1513</v>
       </c>
       <c r="C720" s="2" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="D720" s="3" t="s">
         <v>1539</v>
@@ -15957,10 +16014,10 @@
         <v>1477</v>
       </c>
       <c r="B721" s="2" t="s">
-        <v>1518</v>
+        <v>1514</v>
       </c>
       <c r="C721" s="2" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="D721" s="3" t="s">
         <v>1539</v>
@@ -15971,10 +16028,10 @@
         <v>1477</v>
       </c>
       <c r="B722" s="2" t="s">
-        <v>1519</v>
+        <v>1515</v>
       </c>
       <c r="C722" s="2" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="D722" s="3" t="s">
         <v>1539</v>
@@ -15985,10 +16042,10 @@
         <v>1477</v>
       </c>
       <c r="B723" s="2" t="s">
-        <v>1520</v>
+        <v>1516</v>
       </c>
       <c r="C723" s="2" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="D723" s="3" t="s">
         <v>1539</v>
@@ -15999,10 +16056,10 @@
         <v>1477</v>
       </c>
       <c r="B724" s="2" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="C724" s="2" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="D724" s="3" t="s">
         <v>1539</v>
@@ -16013,10 +16070,10 @@
         <v>1477</v>
       </c>
       <c r="B725" s="2" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="C725" s="2" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="D725" s="3" t="s">
         <v>1539</v>
@@ -16027,10 +16084,10 @@
         <v>1477</v>
       </c>
       <c r="B726" s="2" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
       <c r="C726" s="2" t="s">
-        <v>1493</v>
+        <v>1489</v>
       </c>
       <c r="D726" s="3" t="s">
         <v>1539</v>
@@ -16041,10 +16098,10 @@
         <v>1477</v>
       </c>
       <c r="B727" s="2" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="C727" s="2" t="s">
-        <v>1494</v>
+        <v>1490</v>
       </c>
       <c r="D727" s="3" t="s">
         <v>1539</v>
@@ -16055,10 +16112,10 @@
         <v>1477</v>
       </c>
       <c r="B728" s="2" t="s">
-        <v>1525</v>
+        <v>1521</v>
       </c>
       <c r="C728" s="2" t="s">
-        <v>1495</v>
+        <v>1491</v>
       </c>
       <c r="D728" s="3" t="s">
         <v>1539</v>
@@ -16069,10 +16126,10 @@
         <v>1477</v>
       </c>
       <c r="B729" s="2" t="s">
-        <v>1526</v>
+        <v>1522</v>
       </c>
       <c r="C729" s="2" t="s">
-        <v>1496</v>
+        <v>1492</v>
       </c>
       <c r="D729" s="3" t="s">
         <v>1539</v>
@@ -16083,10 +16140,10 @@
         <v>1477</v>
       </c>
       <c r="B730" s="2" t="s">
-        <v>1527</v>
+        <v>1523</v>
       </c>
       <c r="C730" s="2" t="s">
-        <v>1497</v>
+        <v>1493</v>
       </c>
       <c r="D730" s="3" t="s">
         <v>1539</v>
@@ -16097,10 +16154,10 @@
         <v>1477</v>
       </c>
       <c r="B731" s="2" t="s">
-        <v>1528</v>
+        <v>1524</v>
       </c>
       <c r="C731" s="2" t="s">
-        <v>1498</v>
+        <v>1494</v>
       </c>
       <c r="D731" s="3" t="s">
         <v>1539</v>
@@ -16111,10 +16168,10 @@
         <v>1477</v>
       </c>
       <c r="B732" s="2" t="s">
-        <v>1529</v>
+        <v>1525</v>
       </c>
       <c r="C732" s="2" t="s">
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="D732" s="3" t="s">
         <v>1539</v>
@@ -16125,10 +16182,10 @@
         <v>1477</v>
       </c>
       <c r="B733" s="2" t="s">
-        <v>1530</v>
+        <v>1526</v>
       </c>
       <c r="C733" s="2" t="s">
-        <v>1500</v>
+        <v>1496</v>
       </c>
       <c r="D733" s="3" t="s">
         <v>1539</v>
@@ -16139,10 +16196,10 @@
         <v>1477</v>
       </c>
       <c r="B734" s="2" t="s">
-        <v>1531</v>
+        <v>1527</v>
       </c>
       <c r="C734" s="2" t="s">
-        <v>1501</v>
+        <v>1497</v>
       </c>
       <c r="D734" s="3" t="s">
         <v>1539</v>
@@ -16153,10 +16210,10 @@
         <v>1477</v>
       </c>
       <c r="B735" s="2" t="s">
-        <v>1532</v>
+        <v>1528</v>
       </c>
       <c r="C735" s="2" t="s">
-        <v>1502</v>
+        <v>1498</v>
       </c>
       <c r="D735" s="3" t="s">
         <v>1539</v>
@@ -16167,10 +16224,10 @@
         <v>1477</v>
       </c>
       <c r="B736" s="2" t="s">
-        <v>1533</v>
+        <v>1529</v>
       </c>
       <c r="C736" s="2" t="s">
-        <v>1503</v>
+        <v>1499</v>
       </c>
       <c r="D736" s="3" t="s">
         <v>1539</v>
@@ -16181,10 +16238,10 @@
         <v>1477</v>
       </c>
       <c r="B737" s="2" t="s">
-        <v>1534</v>
+        <v>1530</v>
       </c>
       <c r="C737" s="2" t="s">
-        <v>1504</v>
+        <v>1500</v>
       </c>
       <c r="D737" s="3" t="s">
         <v>1539</v>
@@ -16195,10 +16252,10 @@
         <v>1477</v>
       </c>
       <c r="B738" s="2" t="s">
-        <v>1535</v>
+        <v>1531</v>
       </c>
       <c r="C738" s="2" t="s">
-        <v>1505</v>
+        <v>1501</v>
       </c>
       <c r="D738" s="3" t="s">
         <v>1539</v>
@@ -16209,10 +16266,10 @@
         <v>1477</v>
       </c>
       <c r="B739" s="2" t="s">
-        <v>1536</v>
+        <v>1532</v>
       </c>
       <c r="C739" s="2" t="s">
-        <v>1506</v>
+        <v>1502</v>
       </c>
       <c r="D739" s="3" t="s">
         <v>1539</v>
@@ -16223,10 +16280,10 @@
         <v>1477</v>
       </c>
       <c r="B740" s="2" t="s">
-        <v>1537</v>
+        <v>1533</v>
       </c>
       <c r="C740" s="2" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="D740" s="3" t="s">
         <v>1539</v>
@@ -16237,10 +16294,10 @@
         <v>1477</v>
       </c>
       <c r="B741" s="2" t="s">
-        <v>1538</v>
+        <v>1534</v>
       </c>
       <c r="C741" s="2" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="D741" s="3" t="s">
         <v>1539</v>
@@ -16248,13 +16305,13 @@
     </row>
     <row r="742" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B742" s="2" t="s">
-        <v>1479</v>
+        <v>1535</v>
       </c>
       <c r="C742" s="2" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
       <c r="D742" s="3" t="s">
         <v>1539</v>
@@ -16262,58 +16319,58 @@
     </row>
     <row r="743" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
-        <v>1595</v>
+        <v>1477</v>
       </c>
       <c r="B743" s="2" t="s">
-        <v>1597</v>
+        <v>1536</v>
       </c>
       <c r="C743" s="2" t="s">
-        <v>1604</v>
+        <v>1506</v>
       </c>
       <c r="D743" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="744" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
-        <v>1595</v>
+        <v>1477</v>
       </c>
       <c r="B744" s="2" t="s">
-        <v>1598</v>
+        <v>1537</v>
       </c>
       <c r="C744" s="2" t="s">
-        <v>1605</v>
+        <v>1507</v>
       </c>
       <c r="D744" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
-        <v>1595</v>
+        <v>1477</v>
       </c>
       <c r="B745" s="2" t="s">
-        <v>1599</v>
+        <v>1538</v>
       </c>
       <c r="C745" s="2" t="s">
-        <v>1606</v>
+        <v>1508</v>
       </c>
       <c r="D745" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
-        <v>1595</v>
+        <v>1478</v>
       </c>
       <c r="B746" s="2" t="s">
-        <v>1600</v>
+        <v>1479</v>
       </c>
       <c r="C746" s="2" t="s">
-        <v>1607</v>
+        <v>1509</v>
       </c>
       <c r="D746" s="3" t="s">
-        <v>1596</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.25">
@@ -16321,10 +16378,10 @@
         <v>1595</v>
       </c>
       <c r="B747" s="2" t="s">
-        <v>1601</v>
+        <v>1597</v>
       </c>
       <c r="C747" s="2" t="s">
-        <v>1608</v>
+        <v>1604</v>
       </c>
       <c r="D747" s="3" t="s">
         <v>1596</v>
@@ -16335,10 +16392,10 @@
         <v>1595</v>
       </c>
       <c r="B748" s="2" t="s">
-        <v>1602</v>
+        <v>1598</v>
       </c>
       <c r="C748" s="2" t="s">
-        <v>1609</v>
+        <v>1605</v>
       </c>
       <c r="D748" s="3" t="s">
         <v>1596</v>
@@ -16349,10 +16406,10 @@
         <v>1595</v>
       </c>
       <c r="B749" s="2" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="C749" s="2" t="s">
-        <v>1610</v>
+        <v>1606</v>
       </c>
       <c r="D749" s="3" t="s">
         <v>1596</v>
@@ -16360,58 +16417,58 @@
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B750" s="2" t="s">
-        <v>1612</v>
+        <v>1600</v>
       </c>
       <c r="C750" s="2" t="s">
-        <v>1619</v>
+        <v>1607</v>
       </c>
       <c r="D750" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B751" s="2" t="s">
-        <v>1613</v>
+        <v>1601</v>
       </c>
       <c r="C751" s="2" t="s">
-        <v>1620</v>
+        <v>1608</v>
       </c>
       <c r="D751" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B752" s="2" t="s">
-        <v>1614</v>
+        <v>1602</v>
       </c>
       <c r="C752" s="2" t="s">
-        <v>1621</v>
+        <v>1609</v>
       </c>
       <c r="D752" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
-        <v>1611</v>
+        <v>1595</v>
       </c>
       <c r="B753" s="2" t="s">
-        <v>1615</v>
+        <v>1603</v>
       </c>
       <c r="C753" s="2" t="s">
-        <v>1622</v>
+        <v>1610</v>
       </c>
       <c r="D753" s="3" t="s">
-        <v>1628</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.25">
@@ -16419,10 +16476,10 @@
         <v>1611</v>
       </c>
       <c r="B754" s="2" t="s">
-        <v>1616</v>
+        <v>1612</v>
       </c>
       <c r="C754" s="2" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="D754" s="3" t="s">
         <v>1628</v>
@@ -16433,10 +16490,10 @@
         <v>1611</v>
       </c>
       <c r="B755" s="2" t="s">
-        <v>1625</v>
+        <v>1613</v>
       </c>
       <c r="C755" s="2" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
       <c r="D755" s="3" t="s">
         <v>1628</v>
@@ -16447,10 +16504,10 @@
         <v>1611</v>
       </c>
       <c r="B756" s="2" t="s">
-        <v>1617</v>
+        <v>1614</v>
       </c>
       <c r="C756" s="2" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="D756" s="3" t="s">
         <v>1628</v>
@@ -16461,10 +16518,10 @@
         <v>1611</v>
       </c>
       <c r="B757" s="2" t="s">
-        <v>1618</v>
+        <v>1615</v>
       </c>
       <c r="C757" s="2" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
       <c r="D757" s="3" t="s">
         <v>1628</v>
@@ -16472,72 +16529,72 @@
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
-        <v>1635</v>
+        <v>1611</v>
       </c>
       <c r="B758" s="2" t="s">
-        <v>1636</v>
+        <v>1616</v>
       </c>
       <c r="C758" s="2" t="s">
-        <v>1637</v>
+        <v>1623</v>
       </c>
       <c r="D758" s="3" t="s">
-        <v>1638</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
-        <v>1639</v>
+        <v>1611</v>
       </c>
       <c r="B759" s="2" t="s">
-        <v>1640</v>
+        <v>1625</v>
       </c>
       <c r="C759" s="2" t="s">
-        <v>1641</v>
+        <v>1624</v>
       </c>
       <c r="D759" s="3" t="s">
-        <v>1713</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
-        <v>1639</v>
+        <v>1611</v>
       </c>
       <c r="B760" s="2" t="s">
-        <v>1640</v>
+        <v>1617</v>
       </c>
       <c r="C760" s="2" t="s">
-        <v>1642</v>
+        <v>1626</v>
       </c>
       <c r="D760" s="3" t="s">
-        <v>1713</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
-        <v>1639</v>
+        <v>1611</v>
       </c>
       <c r="B761" s="2" t="s">
-        <v>1640</v>
+        <v>1618</v>
       </c>
       <c r="C761" s="2" t="s">
-        <v>1643</v>
+        <v>1627</v>
       </c>
       <c r="D761" s="3" t="s">
-        <v>1713</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
-        <v>1639</v>
+        <v>1635</v>
       </c>
       <c r="B762" s="2" t="s">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="C762" s="2" t="s">
-        <v>1644</v>
+        <v>1637</v>
       </c>
       <c r="D762" s="3" t="s">
-        <v>1713</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.25">
@@ -16548,7 +16605,7 @@
         <v>1640</v>
       </c>
       <c r="C763" s="2" t="s">
-        <v>1645</v>
+        <v>1641</v>
       </c>
       <c r="D763" s="3" t="s">
         <v>1713</v>
@@ -16556,13 +16613,13 @@
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
-        <v>1717</v>
+        <v>1639</v>
       </c>
       <c r="B764" s="2" t="s">
-        <v>1646</v>
+        <v>1640</v>
       </c>
       <c r="C764" s="2" t="s">
-        <v>1647</v>
+        <v>1642</v>
       </c>
       <c r="D764" s="3" t="s">
         <v>1713</v>
@@ -16570,58 +16627,58 @@
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
-        <v>1718</v>
+        <v>1639</v>
       </c>
       <c r="B765" s="2" t="s">
-        <v>1649</v>
+        <v>1640</v>
       </c>
       <c r="C765" s="2" t="s">
-        <v>1653</v>
+        <v>1643</v>
       </c>
       <c r="D765" s="3" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
-        <v>1718</v>
+        <v>1639</v>
       </c>
       <c r="B766" s="2" t="s">
-        <v>1650</v>
+        <v>1640</v>
       </c>
       <c r="C766" s="2" t="s">
-        <v>1654</v>
+        <v>1644</v>
       </c>
       <c r="D766" s="3" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
-        <v>1718</v>
+        <v>1639</v>
       </c>
       <c r="B767" s="2" t="s">
-        <v>1648</v>
+        <v>1640</v>
       </c>
       <c r="C767" s="2" t="s">
-        <v>1655</v>
+        <v>1645</v>
       </c>
       <c r="D767" s="3" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="768" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="B768" s="2" t="s">
-        <v>1651</v>
+        <v>1646</v>
       </c>
       <c r="C768" s="2" t="s">
-        <v>1656</v>
+        <v>1647</v>
       </c>
       <c r="D768" s="3" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="769" spans="1:4" x14ac:dyDescent="0.25">
@@ -16629,10 +16686,10 @@
         <v>1718</v>
       </c>
       <c r="B769" s="2" t="s">
-        <v>1652</v>
+        <v>1649</v>
       </c>
       <c r="C769" s="2" t="s">
-        <v>1657</v>
+        <v>1653</v>
       </c>
       <c r="D769" s="3" t="s">
         <v>1714</v>
@@ -16640,58 +16697,58 @@
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="B770" s="2" t="s">
-        <v>1659</v>
+        <v>1650</v>
       </c>
       <c r="C770" s="2" t="s">
-        <v>1685</v>
+        <v>1654</v>
       </c>
       <c r="D770" s="3" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="771" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="B771" s="2" t="s">
-        <v>1660</v>
+        <v>1648</v>
       </c>
       <c r="C771" s="2" t="s">
-        <v>1686</v>
+        <v>1655</v>
       </c>
       <c r="D771" s="3" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="772" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="B772" s="2" t="s">
-        <v>1658</v>
+        <v>1651</v>
       </c>
       <c r="C772" s="2" t="s">
-        <v>1687</v>
+        <v>1656</v>
       </c>
       <c r="D772" s="3" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="773" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
-        <v>1712</v>
+        <v>1718</v>
       </c>
       <c r="B773" s="2" t="s">
-        <v>1661</v>
+        <v>1652</v>
       </c>
       <c r="C773" s="2" t="s">
-        <v>1688</v>
+        <v>1657</v>
       </c>
       <c r="D773" s="3" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="774" spans="1:4" x14ac:dyDescent="0.25">
@@ -16699,10 +16756,10 @@
         <v>1712</v>
       </c>
       <c r="B774" s="2" t="s">
-        <v>1662</v>
+        <v>1815</v>
       </c>
       <c r="C774" s="2" t="s">
-        <v>1689</v>
+        <v>1816</v>
       </c>
       <c r="D774" s="3" t="s">
         <v>1713</v>
@@ -16713,10 +16770,10 @@
         <v>1712</v>
       </c>
       <c r="B775" s="2" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
       <c r="C775" s="2" t="s">
-        <v>1690</v>
+        <v>1685</v>
       </c>
       <c r="D775" s="3" t="s">
         <v>1713</v>
@@ -16727,10 +16784,10 @@
         <v>1712</v>
       </c>
       <c r="B776" s="2" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
       <c r="C776" s="2" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
       <c r="D776" s="3" t="s">
         <v>1713</v>
@@ -16741,10 +16798,10 @@
         <v>1712</v>
       </c>
       <c r="B777" s="2" t="s">
-        <v>1665</v>
+        <v>1658</v>
       </c>
       <c r="C777" s="2" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
       <c r="D777" s="3" t="s">
         <v>1713</v>
@@ -16755,10 +16812,10 @@
         <v>1712</v>
       </c>
       <c r="B778" s="2" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="C778" s="2" t="s">
-        <v>1693</v>
+        <v>1688</v>
       </c>
       <c r="D778" s="3" t="s">
         <v>1713</v>
@@ -16769,10 +16826,10 @@
         <v>1712</v>
       </c>
       <c r="B779" s="2" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
       <c r="C779" s="2" t="s">
-        <v>1694</v>
+        <v>1689</v>
       </c>
       <c r="D779" s="3" t="s">
         <v>1713</v>
@@ -16783,10 +16840,10 @@
         <v>1712</v>
       </c>
       <c r="B780" s="2" t="s">
-        <v>1668</v>
+        <v>1663</v>
       </c>
       <c r="C780" s="2" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="D780" s="3" t="s">
         <v>1713</v>
@@ -16797,10 +16854,10 @@
         <v>1712</v>
       </c>
       <c r="B781" s="2" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
       <c r="C781" s="2" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
       <c r="D781" s="3" t="s">
         <v>1713</v>
@@ -16811,10 +16868,10 @@
         <v>1712</v>
       </c>
       <c r="B782" s="2" t="s">
-        <v>1670</v>
+        <v>1665</v>
       </c>
       <c r="C782" s="2" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
       <c r="D782" s="3" t="s">
         <v>1713</v>
@@ -16825,10 +16882,10 @@
         <v>1712</v>
       </c>
       <c r="B783" s="2" t="s">
-        <v>1671</v>
+        <v>1666</v>
       </c>
       <c r="C783" s="2" t="s">
-        <v>1698</v>
+        <v>1693</v>
       </c>
       <c r="D783" s="3" t="s">
         <v>1713</v>
@@ -16839,10 +16896,10 @@
         <v>1712</v>
       </c>
       <c r="B784" s="2" t="s">
-        <v>1672</v>
+        <v>1667</v>
       </c>
       <c r="C784" s="2" t="s">
-        <v>1699</v>
+        <v>1694</v>
       </c>
       <c r="D784" s="3" t="s">
         <v>1713</v>
@@ -16853,10 +16910,10 @@
         <v>1712</v>
       </c>
       <c r="B785" s="2" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
       <c r="C785" s="2" t="s">
-        <v>1700</v>
+        <v>1695</v>
       </c>
       <c r="D785" s="3" t="s">
         <v>1713</v>
@@ -16867,10 +16924,10 @@
         <v>1712</v>
       </c>
       <c r="B786" s="2" t="s">
-        <v>1674</v>
+        <v>1669</v>
       </c>
       <c r="C786" s="2" t="s">
-        <v>1701</v>
+        <v>1696</v>
       </c>
       <c r="D786" s="3" t="s">
         <v>1713</v>
@@ -16881,10 +16938,10 @@
         <v>1712</v>
       </c>
       <c r="B787" s="2" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
       <c r="C787" s="2" t="s">
-        <v>1702</v>
+        <v>1697</v>
       </c>
       <c r="D787" s="3" t="s">
         <v>1713</v>
@@ -16895,10 +16952,10 @@
         <v>1712</v>
       </c>
       <c r="B788" s="2" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
       <c r="C788" s="2" t="s">
-        <v>1703</v>
+        <v>1698</v>
       </c>
       <c r="D788" s="3" t="s">
         <v>1713</v>
@@ -16909,10 +16966,10 @@
         <v>1712</v>
       </c>
       <c r="B789" s="2" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="C789" s="2" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
       <c r="D789" s="3" t="s">
         <v>1713</v>
@@ -16923,10 +16980,10 @@
         <v>1712</v>
       </c>
       <c r="B790" s="2" t="s">
-        <v>1678</v>
+        <v>1673</v>
       </c>
       <c r="C790" s="2" t="s">
-        <v>1705</v>
+        <v>1700</v>
       </c>
       <c r="D790" s="3" t="s">
         <v>1713</v>
@@ -16937,10 +16994,10 @@
         <v>1712</v>
       </c>
       <c r="B791" s="2" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="C791" s="2" t="s">
-        <v>1706</v>
+        <v>1701</v>
       </c>
       <c r="D791" s="3" t="s">
         <v>1713</v>
@@ -16951,10 +17008,10 @@
         <v>1712</v>
       </c>
       <c r="B792" s="2" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
       <c r="C792" s="2" t="s">
-        <v>1707</v>
+        <v>1702</v>
       </c>
       <c r="D792" s="3" t="s">
         <v>1713</v>
@@ -16965,10 +17022,10 @@
         <v>1712</v>
       </c>
       <c r="B793" s="2" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
       <c r="C793" s="2" t="s">
-        <v>1708</v>
+        <v>1703</v>
       </c>
       <c r="D793" s="3" t="s">
         <v>1713</v>
@@ -16979,10 +17036,10 @@
         <v>1712</v>
       </c>
       <c r="B794" s="2" t="s">
-        <v>1682</v>
+        <v>1677</v>
       </c>
       <c r="C794" s="2" t="s">
-        <v>1709</v>
+        <v>1704</v>
       </c>
       <c r="D794" s="3" t="s">
         <v>1713</v>
@@ -16993,10 +17050,10 @@
         <v>1712</v>
       </c>
       <c r="B795" s="2" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
       <c r="C795" s="2" t="s">
-        <v>1710</v>
+        <v>1705</v>
       </c>
       <c r="D795" s="3" t="s">
         <v>1713</v>
@@ -17007,10 +17064,10 @@
         <v>1712</v>
       </c>
       <c r="B796" s="2" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
       <c r="C796" s="2" t="s">
-        <v>1711</v>
+        <v>1706</v>
       </c>
       <c r="D796" s="3" t="s">
         <v>1713</v>
@@ -17021,10 +17078,10 @@
         <v>1712</v>
       </c>
       <c r="B797" s="2" t="s">
-        <v>1730</v>
+        <v>1680</v>
       </c>
       <c r="C797" s="2" t="s">
-        <v>1731</v>
+        <v>1707</v>
       </c>
       <c r="D797" s="3" t="s">
         <v>1713</v>
@@ -17035,10 +17092,10 @@
         <v>1712</v>
       </c>
       <c r="B798" s="2" t="s">
-        <v>1729</v>
+        <v>1681</v>
       </c>
       <c r="C798" s="2" t="s">
-        <v>1732</v>
+        <v>1708</v>
       </c>
       <c r="D798" s="3" t="s">
         <v>1713</v>
@@ -17046,13 +17103,13 @@
     </row>
     <row r="799" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A799" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="B799" s="2" t="s">
-        <v>1720</v>
+        <v>1682</v>
       </c>
       <c r="C799" s="2" t="s">
-        <v>1733</v>
+        <v>1709</v>
       </c>
       <c r="D799" s="3" t="s">
         <v>1713</v>
@@ -17060,13 +17117,13 @@
     </row>
     <row r="800" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A800" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="B800" s="2" t="s">
-        <v>1721</v>
+        <v>1683</v>
       </c>
       <c r="C800" s="2" t="s">
-        <v>1734</v>
+        <v>1710</v>
       </c>
       <c r="D800" s="3" t="s">
         <v>1713</v>
@@ -17074,13 +17131,13 @@
     </row>
     <row r="801" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A801" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="B801" s="2" t="s">
-        <v>1722</v>
+        <v>1684</v>
       </c>
       <c r="C801" s="2" t="s">
-        <v>1735</v>
+        <v>1711</v>
       </c>
       <c r="D801" s="3" t="s">
         <v>1713</v>
@@ -17088,13 +17145,13 @@
     </row>
     <row r="802" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A802" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="B802" s="2" t="s">
-        <v>1723</v>
+        <v>1730</v>
       </c>
       <c r="C802" s="2" t="s">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="D802" s="3" t="s">
         <v>1713</v>
@@ -17102,13 +17159,13 @@
     </row>
     <row r="803" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A803" s="1" t="s">
-        <v>1719</v>
+        <v>1712</v>
       </c>
       <c r="B803" s="2" t="s">
-        <v>1724</v>
+        <v>1729</v>
       </c>
       <c r="C803" s="2" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
       <c r="D803" s="3" t="s">
         <v>1713</v>
@@ -17119,10 +17176,10 @@
         <v>1719</v>
       </c>
       <c r="B804" s="2" t="s">
-        <v>1725</v>
+        <v>1720</v>
       </c>
       <c r="C804" s="2" t="s">
-        <v>1738</v>
+        <v>1733</v>
       </c>
       <c r="D804" s="3" t="s">
         <v>1713</v>
@@ -17133,10 +17190,10 @@
         <v>1719</v>
       </c>
       <c r="B805" s="2" t="s">
-        <v>1726</v>
+        <v>1721</v>
       </c>
       <c r="C805" s="2" t="s">
-        <v>1739</v>
+        <v>1734</v>
       </c>
       <c r="D805" s="3" t="s">
         <v>1713</v>
@@ -17147,10 +17204,10 @@
         <v>1719</v>
       </c>
       <c r="B806" s="2" t="s">
-        <v>1727</v>
+        <v>1722</v>
       </c>
       <c r="C806" s="2" t="s">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="D806" s="3" t="s">
         <v>1713</v>
@@ -17161,10 +17218,10 @@
         <v>1719</v>
       </c>
       <c r="B807" s="2" t="s">
-        <v>1728</v>
+        <v>1723</v>
       </c>
       <c r="C807" s="2" t="s">
-        <v>1741</v>
+        <v>1736</v>
       </c>
       <c r="D807" s="3" t="s">
         <v>1713</v>
@@ -17172,226 +17229,338 @@
     </row>
     <row r="808" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A808" s="1" t="s">
-        <v>1742</v>
+        <v>1719</v>
       </c>
       <c r="B808" s="2" t="s">
-        <v>1743</v>
+        <v>1724</v>
       </c>
       <c r="C808" s="2" t="s">
-        <v>1769</v>
+        <v>1737</v>
       </c>
       <c r="D808" s="3" t="s">
-        <v>1746</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="809" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A809" s="1" t="s">
-        <v>1742</v>
+        <v>1719</v>
       </c>
       <c r="B809" s="2" t="s">
-        <v>1744</v>
+        <v>1725</v>
       </c>
       <c r="C809" s="2" t="s">
-        <v>1770</v>
+        <v>1738</v>
       </c>
       <c r="D809" s="3" t="s">
-        <v>1746</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="810" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A810" s="1" t="s">
-        <v>1742</v>
+        <v>1719</v>
       </c>
       <c r="B810" s="2" t="s">
-        <v>1745</v>
+        <v>1726</v>
       </c>
       <c r="C810" s="2" t="s">
-        <v>1771</v>
+        <v>1739</v>
       </c>
       <c r="D810" s="3" t="s">
-        <v>1746</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="811" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A811" s="1" t="s">
-        <v>1747</v>
+        <v>1719</v>
       </c>
       <c r="B811" s="2" t="s">
-        <v>1754</v>
+        <v>1727</v>
       </c>
       <c r="C811" s="2" t="s">
-        <v>1749</v>
+        <v>1740</v>
       </c>
       <c r="D811" s="3" t="s">
-        <v>1748</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="812" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A812" s="1" t="s">
-        <v>1747</v>
+        <v>1719</v>
       </c>
       <c r="B812" s="2" t="s">
-        <v>1755</v>
+        <v>1728</v>
       </c>
       <c r="C812" s="2" t="s">
-        <v>1750</v>
+        <v>1741</v>
       </c>
       <c r="D812" s="3" t="s">
-        <v>1748</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="813" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A813" s="1" t="s">
-        <v>1747</v>
+        <v>1742</v>
       </c>
       <c r="B813" s="2" t="s">
-        <v>1756</v>
+        <v>1743</v>
       </c>
       <c r="C813" s="2" t="s">
-        <v>1751</v>
+        <v>1769</v>
       </c>
       <c r="D813" s="3" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="814" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A814" s="1" t="s">
-        <v>1752</v>
+        <v>1742</v>
       </c>
       <c r="B814" s="2" t="s">
-        <v>1757</v>
+        <v>1744</v>
       </c>
       <c r="C814" s="2" t="s">
-        <v>1753</v>
+        <v>1770</v>
       </c>
       <c r="D814" s="3" t="s">
-        <v>1764</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="815" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A815" s="1" t="s">
-        <v>1752</v>
+        <v>1742</v>
       </c>
       <c r="B815" s="2" t="s">
-        <v>1758</v>
+        <v>1745</v>
       </c>
       <c r="C815" s="2" t="s">
-        <v>1761</v>
+        <v>1771</v>
       </c>
       <c r="D815" s="3" t="s">
-        <v>1764</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="816" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A816" s="1" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="B816" s="2" t="s">
-        <v>1759</v>
+        <v>1754</v>
       </c>
       <c r="C816" s="2" t="s">
-        <v>1762</v>
+        <v>1749</v>
       </c>
       <c r="D816" s="3" t="s">
-        <v>1764</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="817" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A817" s="1" t="s">
-        <v>1752</v>
+        <v>1747</v>
       </c>
       <c r="B817" s="2" t="s">
-        <v>1760</v>
+        <v>1755</v>
       </c>
       <c r="C817" s="2" t="s">
-        <v>1763</v>
+        <v>1750</v>
       </c>
       <c r="D817" s="3" t="s">
-        <v>1764</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="818" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A818" s="1" t="s">
-        <v>1772</v>
+        <v>1747</v>
       </c>
       <c r="B818" s="2" t="s">
-        <v>1773</v>
+        <v>1756</v>
       </c>
       <c r="C818" s="2" t="s">
-        <v>1775</v>
+        <v>1751</v>
       </c>
       <c r="D818" s="3" t="s">
-        <v>1777</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="819" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A819" s="1" t="s">
-        <v>1772</v>
+        <v>1752</v>
       </c>
       <c r="B819" s="2" t="s">
-        <v>1774</v>
+        <v>1757</v>
       </c>
       <c r="C819" s="2" t="s">
-        <v>1776</v>
+        <v>1753</v>
       </c>
       <c r="D819" s="3" t="s">
-        <v>1777</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="820" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A820" s="1" t="s">
-        <v>1790</v>
+        <v>1752</v>
       </c>
       <c r="B820" s="2" t="s">
-        <v>1791</v>
+        <v>1758</v>
       </c>
       <c r="C820" s="2" t="s">
-        <v>1795</v>
+        <v>1761</v>
       </c>
       <c r="D820" s="3" t="s">
-        <v>1799</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="821" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A821" s="1" t="s">
-        <v>1790</v>
+        <v>1752</v>
       </c>
       <c r="B821" s="2" t="s">
-        <v>1792</v>
+        <v>1759</v>
       </c>
       <c r="C821" s="2" t="s">
-        <v>1796</v>
+        <v>1762</v>
       </c>
       <c r="D821" s="3" t="s">
-        <v>1799</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="822" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A822" s="1" t="s">
-        <v>1790</v>
+        <v>1752</v>
       </c>
       <c r="B822" s="2" t="s">
-        <v>1793</v>
+        <v>1760</v>
       </c>
       <c r="C822" s="2" t="s">
-        <v>1797</v>
+        <v>1763</v>
       </c>
       <c r="D822" s="3" t="s">
-        <v>1799</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="823" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A823" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B823" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C823" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D823" s="3" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A824" s="1" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B824" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C824" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D824" s="3" t="s">
+        <v>1777</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A825" s="1" t="s">
         <v>1790</v>
       </c>
-      <c r="B823" s="2" t="s">
+      <c r="B825" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="C825" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D825" s="3" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A826" s="1" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B826" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C826" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D826" s="3" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A827" s="1" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B827" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C827" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="D827" s="3" t="s">
+        <v>1799</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A828" s="1" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B828" s="2" t="s">
         <v>1794</v>
       </c>
-      <c r="C823" s="2" t="s">
+      <c r="C828" s="2" t="s">
         <v>1798</v>
       </c>
-      <c r="D823" s="3" t="s">
+      <c r="D828" s="3" t="s">
         <v>1799</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A829" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B829" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C829" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D829" s="3" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A830" s="1" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B830" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C830" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="D830" s="3" t="s">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A831" s="1" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B831" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C831" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="D831" s="3" t="s">
+        <v>1814</v>
       </c>
     </row>
   </sheetData>
